--- a/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
+++ b/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\colombres\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB0F7F9-75AF-4A10-ABA8-056D216C4DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DEDB0F-D584-415A-B892-244828891559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$120</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="178">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -484,33 +484,18 @@
     <t>Titular: CONS. DE PROPIETARIOS COLOMBRES 360 Banco: SUPERVIELLE Sucursal: Lomas de Zamora CBU: 02700151 10040979780018 Nº de cuenta: 04097978-001 Código de Pago Electrónico: abonar con los centavos de la UF</t>
   </si>
   <si>
-    <t>Mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>Fotocopias - tauge</t>
   </si>
   <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
   </si>
   <si>
-    <t>VTO 14/11</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza -  Mes de OCTUBRE</t>
-  </si>
-  <si>
     <t>Debito 06/10</t>
   </si>
   <si>
-    <t>Transf 07/10</t>
-  </si>
-  <si>
     <t>Debito 08/10</t>
   </si>
   <si>
-    <t>Transf 14/10</t>
-  </si>
-  <si>
     <t>Transf 13/10</t>
   </si>
   <si>
@@ -527,18 +512,6 @@
   </si>
   <si>
     <t>Transf 17/10</t>
-  </si>
-  <si>
-    <t>Se debe octubre</t>
-  </si>
-  <si>
-    <t>Frank Matias Wallace - Mantenimiento ascensor - Se debe OCTUBRE</t>
-  </si>
-  <si>
-    <t>TecnoComp - Pagado por 3A - REPARACION ESTABILIZADOR PC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TecnoComp - Pagado por 3A - CAMBIO DE DISCO RIGIDO 1 TB Y CONFIGURACION DVR </t>
   </si>
   <si>
     <t>Claudia Guidobono</t>
@@ -552,6 +525,45 @@
   </si>
   <si>
     <t>Diego Varas</t>
+  </si>
+  <si>
+    <t>VTO 15/12</t>
+  </si>
+  <si>
+    <t>Se debe NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor - Se debe NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza -  Mes de NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Servicio de fumigacion - Ortega Daniel</t>
+  </si>
+  <si>
+    <t>Transf 18/11</t>
+  </si>
+  <si>
+    <t>Transf 13/11</t>
+  </si>
+  <si>
+    <t>Transf 11/11</t>
+  </si>
+  <si>
+    <t>Triñares Marta - informe patologias piso 13</t>
+  </si>
+  <si>
+    <t>Cerrajeria Ayram</t>
+  </si>
+  <si>
+    <t>Sobres oficio</t>
+  </si>
+  <si>
+    <t>Tecnocomp - reparacion estabilizador PC</t>
   </si>
 </sst>
 </file>
@@ -1188,7 +1200,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1393,11 +1405,52 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1407,47 +1460,29 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1461,9 +1496,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1473,9 +1505,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1491,17 +1520,20 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1857,20 +1889,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="126" t="s">
         <v>122</v>
       </c>
@@ -1878,7 +1910,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="119" t="s">
         <v>124</v>
       </c>
@@ -1886,7 +1918,7 @@
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
     </row>
-    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="119" t="s">
         <v>123</v>
       </c>
@@ -1894,76 +1926,76 @@
       <c r="C3" s="119"/>
       <c r="D3" s="119"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="163" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="152"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="152"/>
-      <c r="B5" s="152"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="163"/>
+      <c r="B5" s="163"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="152"/>
-      <c r="B6" s="152"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="163"/>
+      <c r="B6" s="163"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="152"/>
-      <c r="B7" s="152"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="149" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="149"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="149"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="153" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="162"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="162"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="164" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="153"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="153"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="153"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="153"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="164"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="164"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="164"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="164"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="164"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="164"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="164"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -1971,7 +2003,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
         <v>80</v>
       </c>
@@ -1979,19 +2011,19 @@
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C23" s="113">
         <v>1268327.8999999999</v>
       </c>
       <c r="D23" s="83"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
@@ -2002,7 +2034,7 @@
       </c>
       <c r="D24" s="83"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -2013,14 +2045,14 @@
       <c r="D25" s="83"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="113"/>
       <c r="D26" s="83"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="49" t="s">
         <v>82</v>
       </c>
@@ -2030,26 +2062,26 @@
         <v>992466.6399999999</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="147" t="s">
+      <c r="F27" s="160" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="148"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G27" s="161"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="125" t="s">
         <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C28" s="113">
         <v>971916.1</v>
       </c>
       <c r="D28" s="83"/>
-      <c r="F28" s="147"/>
-      <c r="G28" s="148"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F28" s="160"/>
+      <c r="G28" s="161"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
@@ -2060,7 +2092,7 @@
       <c r="D29" s="83"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
@@ -2071,9 +2103,9 @@
       <c r="D30" s="83"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="109">
@@ -2082,7 +2114,7 @@
       <c r="D31" s="83"/>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="49" t="s">
         <v>82</v>
       </c>
@@ -2093,19 +2125,19 @@
       </c>
       <c r="D32" s="84"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C33" s="113">
         <v>1034599.1</v>
       </c>
       <c r="D33" s="124"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>81</v>
       </c>
@@ -2115,7 +2147,7 @@
       </c>
       <c r="D34" s="124"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>83</v>
       </c>
@@ -2125,13 +2157,13 @@
       </c>
       <c r="D35" s="124"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="109"/>
       <c r="D36" s="124"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="49" t="s">
         <v>82</v>
       </c>
@@ -2142,7 +2174,7 @@
       </c>
       <c r="D37" s="84"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="18" t="s">
         <v>0</v>
       </c>
@@ -2155,7 +2187,7 @@
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
         <v>38</v>
       </c>
@@ -2164,21 +2196,20 @@
       <c r="D39" s="86"/>
       <c r="F39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="58" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="113">
-        <f>35000*3</f>
-        <v>105000</v>
-      </c>
-      <c r="D40" s="145" t="s">
-        <v>159</v>
+      <c r="C40" s="187">
+        <v>70000</v>
+      </c>
+      <c r="D40" s="144" t="s">
+        <v>173</v>
       </c>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="127" t="s">
         <v>133</v>
       </c>
@@ -2186,10 +2217,10 @@
         <v>166</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="145"/>
+      <c r="D41" s="144"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="18" t="s">
         <v>34</v>
       </c>
@@ -2197,10 +2228,10 @@
       <c r="C42" s="31"/>
       <c r="D42" s="85">
         <f>SUM(C40:C41)</f>
-        <v>105000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="25" t="s">
         <v>77</v>
       </c>
@@ -2208,31 +2239,31 @@
       <c r="C43" s="29"/>
       <c r="D43" s="60"/>
     </row>
-    <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="150" t="s">
+    <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="151"/>
+      <c r="B44" s="152"/>
       <c r="C44" s="142">
         <v>175052</v>
       </c>
       <c r="D44" s="110" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="150" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="151" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="151"/>
+      <c r="B45" s="152"/>
       <c r="C45" s="143">
         <v>4203</v>
       </c>
       <c r="D45" s="110" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="18" t="s">
         <v>1</v>
       </c>
@@ -2243,7 +2274,7 @@
         <v>179255</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="27" t="s">
         <v>35</v>
       </c>
@@ -2251,66 +2282,66 @@
       <c r="C47" s="32"/>
       <c r="D47" s="88"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>134</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C48" s="144">
-        <v>1424079.5</v>
+        <v>169</v>
+      </c>
+      <c r="C48" s="186">
+        <v>1298549.8600000001</v>
       </c>
       <c r="D48" s="110" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F48" s="128"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>135</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C49" s="141">
-        <v>16459.22</v>
+        <v>169</v>
+      </c>
+      <c r="C49" s="183">
+        <v>15003.51</v>
       </c>
       <c r="D49" s="110" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>136</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="141">
-        <v>148132.94</v>
+        <v>169</v>
+      </c>
+      <c r="C50" s="183">
+        <v>135031.6</v>
       </c>
       <c r="D50" s="110" t="str">
         <f>D49</f>
         <v>Debito 13/10</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="141">
-        <v>290229.78999999998</v>
+        <v>169</v>
+      </c>
+      <c r="C51" s="183">
+        <v>272601.64</v>
       </c>
       <c r="D51" s="111" t="str">
         <f>D50</f>
         <v>Debito 13/10</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="18" t="s">
         <v>2</v>
       </c>
@@ -2318,10 +2349,10 @@
       <c r="C52" s="33"/>
       <c r="D52" s="87">
         <f>SUM(C48:C51)</f>
-        <v>1878901.45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1721186.6100000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="27" t="s">
         <v>37</v>
       </c>
@@ -2329,69 +2360,81 @@
       <c r="C53" s="32"/>
       <c r="D53" s="88"/>
     </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>138</v>
       </c>
       <c r="B54" s="5"/>
-      <c r="C54" s="141"/>
+      <c r="C54" s="183">
+        <v>507167.57</v>
+      </c>
       <c r="D54" s="138"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="141">
-        <v>35883.19</v>
+      <c r="C55" s="183">
+        <v>26232.46</v>
       </c>
       <c r="D55" s="111" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F55">
         <f>180000+82000</f>
         <v>262000</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>140</v>
       </c>
       <c r="B56" s="5"/>
-      <c r="C56" s="141">
-        <v>728258.14</v>
+      <c r="C56" s="183">
+        <v>675127.84</v>
       </c>
       <c r="D56" s="92" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="159" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="158" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="160"/>
-      <c r="C57" s="141"/>
-      <c r="D57" s="122"/>
-    </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="159"/>
+      <c r="C57" s="183">
+        <v>177521</v>
+      </c>
+      <c r="D57" s="92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B58" s="133"/>
       <c r="C58" s="122">
         <v>262000</v>
       </c>
       <c r="D58" s="122" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="B59" s="116"/>
-      <c r="C59" s="141"/>
-      <c r="D59" s="122"/>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="183">
+        <v>30600</v>
+      </c>
+      <c r="D59" s="122" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="18" t="s">
         <v>3</v>
       </c>
@@ -2399,10 +2442,10 @@
       <c r="C60" s="31"/>
       <c r="D60" s="87">
         <f>SUM(C54:C59)</f>
-        <v>1026141.3300000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1678648.87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="27" t="s">
         <v>36</v>
       </c>
@@ -2410,9 +2453,9 @@
       <c r="C61" s="31"/>
       <c r="D61" s="90"/>
     </row>
-    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B62" s="133"/>
       <c r="C62" s="141">
@@ -2422,406 +2465,438 @@
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="150" t="s">
+    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="B63" s="133"/>
+      <c r="C63" s="183">
+        <v>5600</v>
+      </c>
+      <c r="D63" s="145"/>
+    </row>
+    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="184"/>
+      <c r="B64" s="185"/>
+      <c r="C64" s="183">
+        <v>58500</v>
+      </c>
+      <c r="D64" s="145"/>
+    </row>
+    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="188" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="189"/>
+      <c r="C65" s="183">
+        <v>85000</v>
+      </c>
+      <c r="D65" s="122" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="151" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" s="152"/>
+      <c r="C66" s="183">
+        <v>250000</v>
+      </c>
+      <c r="D66" s="122" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="146" t="s">
+        <v>177</v>
+      </c>
+      <c r="B67" s="147"/>
+      <c r="C67" s="183">
+        <v>15000</v>
+      </c>
+      <c r="D67" s="122"/>
+    </row>
+    <row r="68" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="156" t="s">
         <v>168</v>
       </c>
-      <c r="B63" s="151"/>
-      <c r="C63" s="141">
-        <v>15000</v>
-      </c>
-      <c r="D63" s="146"/>
-    </row>
-    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="150" t="s">
-        <v>169</v>
-      </c>
-      <c r="B64" s="151"/>
-      <c r="C64" s="141">
-        <v>175000</v>
-      </c>
-      <c r="D64" s="146"/>
-    </row>
-    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="157" t="s">
-        <v>155</v>
-      </c>
-      <c r="B65" s="158"/>
-      <c r="C65" s="144">
-        <v>67950</v>
-      </c>
-      <c r="D65" s="122" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
+      <c r="B68" s="157"/>
+      <c r="C68" s="186">
+        <v>68800</v>
+      </c>
+      <c r="D68" s="122" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="27"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="94">
-        <f>SUM(C62:C65)</f>
-        <v>269150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="27" t="s">
+      <c r="B69" s="27"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="94">
+        <f>SUM(C62:C68)</f>
+        <v>494100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B67" s="59"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="90"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
+      <c r="B70" s="59"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="90"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="141">
+      <c r="B71" s="5"/>
+      <c r="C71" s="141">
         <v>56820.35</v>
       </c>
-      <c r="D68" s="95"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
+      <c r="D71" s="95"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="141">
+      <c r="B72" s="5"/>
+      <c r="C72" s="141">
         <v>80545.34</v>
       </c>
-      <c r="D69" s="93"/>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="45" t="s">
+      <c r="D72" s="93"/>
+    </row>
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B70" s="45"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="87">
-        <f>SUM(C68:C69)</f>
+      <c r="B73" s="45"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="87">
+        <f>SUM(C71:C72)</f>
         <v>137365.69</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="83"/>
-      <c r="D71" s="97"/>
-    </row>
-    <row r="72" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="154" t="s">
+    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="83"/>
+      <c r="D74" s="97"/>
+    </row>
+    <row r="75" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="153" t="s">
         <v>147</v>
       </c>
-      <c r="B72" s="155"/>
-      <c r="C72" s="156"/>
-      <c r="D72" s="98">
+      <c r="B75" s="154"/>
+      <c r="C75" s="155"/>
+      <c r="D75" s="98">
         <f>9000000-6763271.11-257950</f>
         <v>1978778.8899999997</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="C73" s="99"/>
-      <c r="D73" s="100"/>
-      <c r="E73" s="40"/>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3" t="s">
+    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="1"/>
+      <c r="C76" s="99"/>
+      <c r="D76" s="100"/>
+      <c r="E76" s="40"/>
+    </row>
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="101"/>
-      <c r="D74" s="102">
-        <f>(SUM(D29:D72))</f>
-        <v>9000000</v>
-      </c>
-      <c r="E74" s="40"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C75" s="99"/>
-      <c r="D75" s="99"/>
-      <c r="F75" s="131"/>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="99"/>
-      <c r="D76" s="99"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="B77" s="10"/>
+      <c r="C77" s="101"/>
+      <c r="D77" s="102">
+        <f>(SUM(D29:D75))</f>
+        <v>9684742.6999999993</v>
+      </c>
+      <c r="E77" s="40"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C78" s="99"/>
+      <c r="D78" s="99"/>
+      <c r="F78" s="131"/>
+    </row>
+    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C79" s="99"/>
+      <c r="D79" s="99"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="103"/>
-      <c r="D77" s="104"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="150"/>
-      <c r="B78" s="151"/>
-      <c r="C78" s="91"/>
-      <c r="D78" s="89"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="150"/>
-      <c r="B79" s="151"/>
-      <c r="C79" s="91"/>
-      <c r="D79" s="89"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="107"/>
-      <c r="B80" s="108"/>
-      <c r="C80" s="91"/>
-      <c r="D80" s="89"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="43"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51">
-        <f>SUM(C78:C80)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="21" t="s">
+      <c r="B80" s="12"/>
+      <c r="C80" s="103"/>
+      <c r="D80" s="104"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="151"/>
+      <c r="B81" s="152"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="89"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="151"/>
+      <c r="B82" s="152"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="89"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="107"/>
+      <c r="B83" s="108"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="89"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="43"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51">
+        <f>SUM(C81:C83)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B84" s="21"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="115"/>
-    </row>
-    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
+      <c r="B87" s="21"/>
+      <c r="C87" s="22"/>
+      <c r="D87" s="115"/>
+    </row>
+    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B86" s="10"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="61">
-        <f>D81+D84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="81" t="s">
+      <c r="B89" s="10"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="61">
+        <f>D84+D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="B88" s="82">
-        <f>D74</f>
-        <v>9000000</v>
-      </c>
-      <c r="C88" s="40"/>
-    </row>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="81" t="s">
+      <c r="B91" s="82">
+        <f>D77</f>
+        <v>9684742.6999999993</v>
+      </c>
+      <c r="C91" s="40"/>
+    </row>
+    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="82">
-        <f>D74-D72</f>
-        <v>7021221.1100000003</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="81" t="s">
+      <c r="B92" s="82">
+        <f>D77-D75</f>
+        <v>7705963.8099999996</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="B90" s="82">
-        <f>D86-D84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="81" t="s">
+      <c r="B93" s="82">
+        <f>D89-D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="B91" s="82">
-        <f>D86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="163"/>
-      <c r="B94" s="163"/>
-      <c r="C94" s="163"/>
-      <c r="D94" s="163"/>
-    </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="163"/>
-      <c r="B95" s="163"/>
-      <c r="C95" s="163"/>
-      <c r="D95" s="163"/>
-    </row>
-    <row r="96" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="163"/>
-      <c r="B96" s="163"/>
-      <c r="C96" s="163"/>
-      <c r="D96" s="163"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="15" t="s">
+      <c r="B94" s="82">
+        <f>D89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="150"/>
+      <c r="B97" s="150"/>
+      <c r="C97" s="150"/>
+      <c r="D97" s="150"/>
+    </row>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="150"/>
+      <c r="B98" s="150"/>
+      <c r="C98" s="150"/>
+      <c r="D98" s="150"/>
+    </row>
+    <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="150"/>
+      <c r="B99" s="150"/>
+      <c r="C99" s="150"/>
+      <c r="D99" s="150"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B98" s="36"/>
-    </row>
-    <row r="99" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="24" t="s">
+      <c r="B101" s="36"/>
+    </row>
+    <row r="102" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B99" s="112">
+      <c r="B102" s="112">
         <v>3268631.95</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="16" t="s">
+    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B100" s="37">
+      <c r="B103" s="37">
         <f>PRORRATEO!H34</f>
-        <v>7504571.0899999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
+        <v>7623071.0899999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B101" s="93">
-        <f>B116</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="17" t="s">
+      <c r="B104" s="93">
+        <f>B119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B102" s="136">
+      <c r="B105" s="136">
         <v>-46641</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="35" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B103" s="93">
-        <f>-B89</f>
-        <v>-7021221.1100000003</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="17" t="s">
+      <c r="B106" s="93">
+        <f>-B92</f>
+        <v>-7705963.8099999996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B104" s="93">
-        <f>-(B90)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="23" t="s">
+      <c r="B107" s="93">
+        <f>-(B93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B105" s="112">
-        <f>SUM(B99:B104)</f>
-        <v>3705340.9299999988</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="38"/>
-      <c r="C106" s="40"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="162" t="s">
+      <c r="B108" s="112">
+        <f>SUM(B102:B107)</f>
+        <v>3139098.2299999995</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B109" s="38"/>
+      <c r="C109" s="40"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="B108" s="162"/>
-    </row>
-    <row r="109" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="162"/>
-      <c r="B109" s="162"/>
-    </row>
-    <row r="110" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="105"/>
-      <c r="B110" s="30"/>
-    </row>
-    <row r="111" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="105"/>
-      <c r="B111" s="30"/>
-    </row>
-    <row r="112" spans="1:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="105"/>
-      <c r="B112" s="30"/>
-    </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="149"/>
+    </row>
+    <row r="112" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="149"/>
+      <c r="B112" s="149"/>
+    </row>
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="105"/>
       <c r="B113" s="30"/>
     </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="105"/>
       <c r="B114" s="30"/>
     </row>
-    <row r="115" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="105"/>
-      <c r="B115" s="129"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="41" t="s">
+      <c r="B115" s="30"/>
+    </row>
+    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="105"/>
+      <c r="B116" s="30"/>
+    </row>
+    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="105"/>
+      <c r="B117" s="30"/>
+    </row>
+    <row r="118" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="105"/>
+      <c r="B118" s="129"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B116" s="106">
-        <f>SUM(B110:B115)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L117" s="8"/>
-    </row>
-    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="161"/>
-      <c r="B118" s="161"/>
-      <c r="C118" s="161"/>
-      <c r="D118" s="161"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="161"/>
-      <c r="B119" s="161"/>
-      <c r="C119" s="161"/>
-      <c r="D119" s="161"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="161"/>
-      <c r="B120" s="161"/>
-      <c r="C120" s="161"/>
-      <c r="D120" s="161"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="161"/>
-      <c r="B121" s="161"/>
-      <c r="C121" s="161"/>
-      <c r="D121" s="161"/>
+      <c r="B119" s="106">
+        <f>SUM(B113:B118)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L120" s="8"/>
+    </row>
+    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="148"/>
+      <c r="B121" s="148"/>
+      <c r="C121" s="148"/>
+      <c r="D121" s="148"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" s="148"/>
+      <c r="B122" s="148"/>
+      <c r="C122" s="148"/>
+      <c r="D122" s="148"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123" s="148"/>
+      <c r="B123" s="148"/>
+      <c r="C123" s="148"/>
+      <c r="D123" s="148"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124" s="148"/>
+      <c r="B124" s="148"/>
+      <c r="C124" s="148"/>
+      <c r="D124" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A118:D121"/>
-    <mergeCell ref="A108:B109"/>
-    <mergeCell ref="A94:D96"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="F27:G28"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A121:D124"/>
+    <mergeCell ref="A111:B112"/>
+    <mergeCell ref="A97:D99"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2832,61 +2907,61 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="0.140625" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.109375" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="171" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2898,18 +2973,18 @@
       <c r="P2" s="47"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="165"/>
-      <c r="I3" s="165"/>
-      <c r="J3" s="165"/>
-      <c r="K3" s="165"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2918,79 +2993,79 @@
       <c r="O3" s="48"/>
       <c r="P3" s="52"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="178" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="168" t="s">
+      <c r="F4" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="168" t="s">
+      <c r="H4" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="168" t="s">
+      <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="173" t="s">
+      <c r="J4" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="170" t="s">
+      <c r="K4" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="170" t="s">
+      <c r="L4" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="170" t="s">
+      <c r="M4" s="176" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="176" t="s">
+      <c r="N4" s="181" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="166" t="s">
+      <c r="P4" s="173" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="179"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="174"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="175"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="177"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="166"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="182"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 14/11</v>
-      </c>
-      <c r="P5" s="167"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/12</v>
+      </c>
+      <c r="P5" s="174"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3045,7 +3120,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3101,10 +3176,10 @@
         <v>0.02</v>
       </c>
       <c r="R7" s="40" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3160,7 +3235,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3220,7 +3295,7 @@
       </c>
       <c r="S9" s="40"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3241,13 +3316,13 @@
         <v>316848.05</v>
       </c>
       <c r="H10" s="64">
-        <f>127000+RESUMEN!C63+RESUMEN!C64</f>
-        <v>317000</v>
+        <f>127000+RESUMEN!C64+RESUMEN!C66</f>
+        <v>435500</v>
       </c>
       <c r="I10" s="65"/>
       <c r="J10" s="66">
         <f t="shared" si="2"/>
-        <v>-151.95000000001164</v>
+        <v>-118651.95000000001</v>
       </c>
       <c r="K10" s="66">
         <f t="shared" si="3"/>
@@ -3266,11 +3341,11 @@
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>409348.05</v>
+        <v>290848.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>421628.05</v>
+        <v>299573.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3278,7 +3353,7 @@
       </c>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3334,7 +3409,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -3392,7 +3467,7 @@
       <c r="R12" s="131"/>
       <c r="S12" s="128"/>
     </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3448,7 +3523,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3505,10 +3580,10 @@
         <v>0.09</v>
       </c>
       <c r="R14" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3564,10 +3639,10 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3624,7 +3699,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3681,7 +3756,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3737,7 +3812,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3793,7 +3868,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3850,7 +3925,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3906,11 +3981,11 @@
         <v>0.16</v>
       </c>
       <c r="R21" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="S21" s="39"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -3967,7 +4042,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4024,7 +4099,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4081,7 +4156,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4141,7 +4216,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4198,7 +4273,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4255,7 +4330,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4312,7 +4387,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4369,7 +4444,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4428,7 +4503,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4489,7 +4564,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4546,7 +4621,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4592,7 +4667,7 @@
       </c>
       <c r="Q33" s="40"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="76"/>
       <c r="C34" s="77"/>
       <c r="D34" s="78"/>
@@ -4607,7 +4682,7 @@
       </c>
       <c r="H34" s="54">
         <f>SUM(H6:H33)</f>
-        <v>7504571.0899999999</v>
+        <v>7623071.0899999999</v>
       </c>
       <c r="I34" s="54">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4629,111 +4704,106 @@
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>11005265.779999999</v>
+        <v>10886765.779999999</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>11335424.779999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11213369.779999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="161" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="161"/>
-      <c r="I37" s="161"/>
-      <c r="J37" s="161"/>
-      <c r="K37" s="161"/>
-      <c r="L37" s="161"/>
-      <c r="M37" s="161"/>
-      <c r="N37" s="161"/>
-      <c r="O37" s="161"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="161"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="161"/>
-      <c r="I39" s="161"/>
-      <c r="J39" s="161"/>
-      <c r="K39" s="161"/>
-      <c r="L39" s="161"/>
-      <c r="M39" s="161"/>
-      <c r="N39" s="161"/>
-      <c r="O39" s="161"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="161"/>
-      <c r="E40" s="161"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="161"/>
-      <c r="I40" s="161"/>
-      <c r="J40" s="161"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="161"/>
-      <c r="M40" s="161"/>
-      <c r="N40" s="161"/>
-      <c r="O40" s="161"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="161"/>
-      <c r="E41" s="161"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="161"/>
-      <c r="I41" s="161"/>
-      <c r="J41" s="161"/>
-      <c r="K41" s="161"/>
-      <c r="L41" s="161"/>
-      <c r="M41" s="161"/>
-      <c r="N41" s="161"/>
-      <c r="O41" s="161"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="161"/>
-      <c r="E42" s="161"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="161"/>
-      <c r="H42" s="161"/>
-      <c r="I42" s="161"/>
-      <c r="J42" s="161"/>
-      <c r="K42" s="161"/>
-      <c r="L42" s="161"/>
-      <c r="M42" s="161"/>
-      <c r="N42" s="161"/>
-      <c r="O42" s="161"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="148" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="148"/>
+      <c r="F37" s="148"/>
+      <c r="G37" s="148"/>
+      <c r="H37" s="148"/>
+      <c r="I37" s="148"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="148"/>
+      <c r="M37" s="148"/>
+      <c r="N37" s="148"/>
+      <c r="O37" s="148"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
+      <c r="F38" s="148"/>
+      <c r="G38" s="148"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="148"/>
+      <c r="J38" s="148"/>
+      <c r="K38" s="148"/>
+      <c r="L38" s="148"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="148"/>
+      <c r="O38" s="148"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="148"/>
+      <c r="E39" s="148"/>
+      <c r="F39" s="148"/>
+      <c r="G39" s="148"/>
+      <c r="H39" s="148"/>
+      <c r="I39" s="148"/>
+      <c r="J39" s="148"/>
+      <c r="K39" s="148"/>
+      <c r="L39" s="148"/>
+      <c r="M39" s="148"/>
+      <c r="N39" s="148"/>
+      <c r="O39" s="148"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="148"/>
+      <c r="E40" s="148"/>
+      <c r="F40" s="148"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="148"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="148"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="148"/>
+      <c r="M40" s="148"/>
+      <c r="N40" s="148"/>
+      <c r="O40" s="148"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="148"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="148"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="148"/>
+      <c r="K41" s="148"/>
+      <c r="L41" s="148"/>
+      <c r="M41" s="148"/>
+      <c r="N41" s="148"/>
+      <c r="O41" s="148"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D42" s="148"/>
+      <c r="E42" s="148"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="148"/>
+      <c r="H42" s="148"/>
+      <c r="I42" s="148"/>
+      <c r="J42" s="148"/>
+      <c r="K42" s="148"/>
+      <c r="L42" s="148"/>
+      <c r="M42" s="148"/>
+      <c r="N42" s="148"/>
+      <c r="O42" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4746,6 +4816,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
+++ b/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\colombres\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DEDB0F-D584-415A-B892-244828891559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AE1835-07CF-44A6-85DB-AA8BBB0E2CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$119</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="185">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -427,9 +427,6 @@
     <t>Calderon Diego Alejandro</t>
   </si>
   <si>
-    <t>Espinola Savoia Pablo Damian</t>
-  </si>
-  <si>
     <t>Honorarios administracion RC</t>
   </si>
   <si>
@@ -488,30 +485,6 @@
   </si>
   <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
-  </si>
-  <si>
-    <t>Debito 06/10</t>
-  </si>
-  <si>
-    <t>Debito 08/10</t>
-  </si>
-  <si>
-    <t>Transf 13/10</t>
-  </si>
-  <si>
-    <t>Liquidacion por Renuncia:</t>
-  </si>
-  <si>
-    <t>Debito 13/10</t>
-  </si>
-  <si>
-    <t>Debito 16/10</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de semaforo y cableado del mismo</t>
-  </si>
-  <si>
-    <t>Transf 17/10</t>
   </si>
   <si>
     <t>Claudia Guidobono</t>
@@ -530,21 +503,12 @@
     <t>VTO 15/12</t>
   </si>
   <si>
-    <t>Se debe NOVIEMBRE</t>
-  </si>
-  <si>
-    <t>Frank Matias Wallace - Mantenimiento ascensor - Se debe NOVIEMBRE</t>
-  </si>
-  <si>
     <t>Articulos de limpieza -  Mes de NOVIEMBRE</t>
   </si>
   <si>
     <t>Mes de OCTUBRE</t>
   </si>
   <si>
-    <t>Servicio de fumigacion - Ortega Daniel</t>
-  </si>
-  <si>
     <t>Transf 18/11</t>
   </si>
   <si>
@@ -554,16 +518,73 @@
     <t>Transf 11/11</t>
   </si>
   <si>
-    <t>Triñares Marta - informe patologias piso 13</t>
-  </si>
-  <si>
-    <t>Cerrajeria Ayram</t>
-  </si>
-  <si>
     <t>Sobres oficio</t>
   </si>
   <si>
-    <t>Tecnocomp - reparacion estabilizador PC</t>
+    <t>Triñares Marta - Informe patologias piso 13</t>
+  </si>
+  <si>
+    <t>Transf 04/11</t>
+  </si>
+  <si>
+    <t>Debito 05/11</t>
+  </si>
+  <si>
+    <t>Debito 07/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrajeria Ayram - Arreglo de bisagra </t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Frank Matias Wallace - Mantenimiento ascensor OCTUBRE</t>
+  </si>
+  <si>
+    <t>Debito 11/11</t>
+  </si>
+  <si>
+    <t>Basile Maria Celeste - Segundo testimonio escribana</t>
+  </si>
+  <si>
+    <t>Transf 14/11</t>
+  </si>
+  <si>
+    <t>Colmeiro Oscar - Arreglo terraza y Atillo</t>
+  </si>
+  <si>
+    <t>Pago parcial 14/11</t>
+  </si>
+  <si>
+    <t>Servicio de fumigacion - Ortega Daniel - Mes de Octubre</t>
+  </si>
+  <si>
+    <t>Transf 25/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra de bordeadora </t>
+  </si>
+  <si>
+    <t>Loschi Bruno - Mantenimiento de gripo electrogeno</t>
+  </si>
+  <si>
+    <t>Transf 26/11</t>
+  </si>
+  <si>
+    <t>Servisur - Cambio de reloj de iluminacion - Mano de obra y material</t>
+  </si>
+  <si>
+    <t>Noviembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octubre </t>
+  </si>
+  <si>
+    <t>Transf 27/11</t>
+  </si>
+  <si>
+    <t>Debito 17/11</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1221,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1368,7 +1389,6 @@
     <xf numFmtId="44" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1394,9 +1414,6 @@
     <xf numFmtId="44" fontId="25" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1415,6 +1432,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1424,46 +1486,46 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,63 +1540,7 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1889,28 +1895,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L123"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="125" t="s">
         <v>122</v>
       </c>
       <c r="B1" s="118"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="119" t="s">
         <v>124</v>
       </c>
@@ -1918,7 +1924,7 @@
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
     </row>
-    <row r="3" spans="1:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="119" t="s">
         <v>123</v>
       </c>
@@ -1926,76 +1932,76 @@
       <c r="C3" s="119"/>
       <c r="D3" s="119"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="152" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="163"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="163"/>
-      <c r="B5" s="163"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="152"/>
+      <c r="B5" s="152"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="163"/>
-      <c r="B6" s="163"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="152"/>
+      <c r="B6" s="152"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="163"/>
-      <c r="B7" s="163"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="152"/>
+      <c r="B7" s="152"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="162" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="162"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="162"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="164" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="149" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="149"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="149"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="164"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="164"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="164"/>
-    </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="164"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="164"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+    </row>
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2003,7 +2009,7 @@
       <c r="C21" s="9"/>
       <c r="D21" s="13"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
         <v>80</v>
       </c>
@@ -2011,892 +2017,903 @@
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C23" s="113">
-        <v>1268327.8999999999</v>
+        <v>1289041</v>
       </c>
       <c r="D23" s="83"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="113">
-        <f>-523977.97+248116.64</f>
-        <v>-275861.32999999996</v>
+        <f>-532535.06+252168.64</f>
+        <v>-280366.42000000004</v>
       </c>
       <c r="D24" s="83"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="113">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="83"/>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="113"/>
       <c r="D26" s="83"/>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="49" t="s">
         <v>82</v>
       </c>
       <c r="B27" s="49"/>
       <c r="C27" s="114">
         <f>SUM(C23:C26)</f>
-        <v>992466.6399999999</v>
+        <v>1008674.64</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="160" t="s">
-        <v>148</v>
-      </c>
-      <c r="G27" s="161"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="125" t="s">
-        <v>132</v>
+      <c r="F27" s="147" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" s="148"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C28" s="113">
-        <v>971916.1</v>
-      </c>
-      <c r="D28" s="83"/>
-      <c r="F28" s="160"/>
-      <c r="G28" s="161"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1126658.44</v>
+      </c>
+      <c r="D28" s="124"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="109">
-        <v>-211391.74</v>
-      </c>
-      <c r="D29" s="83"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C29" s="113">
+        <v>-245048.2</v>
+      </c>
+      <c r="D29" s="124"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="109">
-        <v>0.64</v>
-      </c>
-      <c r="D30" s="83"/>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>156</v>
-      </c>
+      <c r="C30" s="113">
+        <v>0.76</v>
+      </c>
+      <c r="D30" s="124"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="109">
-        <v>862842</v>
-      </c>
-      <c r="D31" s="83"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C31" s="109"/>
+      <c r="D31" s="124"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="49"/>
+      <c r="B32" s="123"/>
       <c r="C32" s="50">
         <f>SUM(C28:C31)</f>
-        <v>1623367</v>
+        <v>881611</v>
       </c>
       <c r="D32" s="84"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C33" s="113">
-        <v>1034599.1</v>
-      </c>
-      <c r="D33" s="124"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="113">
-        <v>-225025.29</v>
-      </c>
-      <c r="D34" s="124"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>83</v>
+    <row r="33" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="85">
+        <f>C27+C32</f>
+        <v>1890285.6400000001</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="86"/>
+      <c r="F34" s="14"/>
+    </row>
+    <row r="35" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="58" t="s">
+        <v>39</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="113">
-        <v>0.19</v>
-      </c>
-      <c r="D35" s="124"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="124"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="123"/>
-      <c r="C37" s="50">
-        <f>SUM(C33:C36)</f>
-        <v>809573.99999999988</v>
-      </c>
-      <c r="D37" s="84"/>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70000</v>
+      </c>
+      <c r="D35" s="142" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="116" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="113">
+        <v>195000</v>
+      </c>
+      <c r="D36" s="142" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="126" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="117" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" s="113">
+        <v>195000</v>
+      </c>
+      <c r="D37" s="142" t="s">
+        <v>183</v>
+      </c>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="18" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B38" s="18"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="31"/>
       <c r="D38" s="85">
-        <f>C27+C32+C37</f>
-        <v>3425407.6399999997</v>
-      </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="86"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="187">
-        <v>70000</v>
-      </c>
-      <c r="D40" s="144" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="127" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="117" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="144"/>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>SUM(C35:C37)</f>
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="60"/>
+    </row>
+    <row r="40" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="151"/>
+      <c r="C40" s="140">
+        <v>175052</v>
+      </c>
+      <c r="D40" s="110" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="150" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="151"/>
+      <c r="C41" s="141">
+        <v>4203</v>
+      </c>
+      <c r="D41" s="110" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="31"/>
-      <c r="D42" s="85">
+      <c r="D42" s="87">
         <f>SUM(C40:C41)</f>
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="60"/>
-    </row>
-    <row r="44" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="151" t="s">
-        <v>128</v>
-      </c>
-      <c r="B44" s="152"/>
-      <c r="C44" s="142">
-        <v>175052</v>
+        <v>179255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="88"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" s="182">
+        <v>1298549.8600000001</v>
       </c>
       <c r="D44" s="110" t="s">
+        <v>166</v>
+      </c>
+      <c r="F44" s="127"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="151" t="s">
-        <v>129</v>
-      </c>
-      <c r="B45" s="152"/>
-      <c r="C45" s="143">
-        <v>4203</v>
+      <c r="C45" s="139">
+        <v>15003.51</v>
       </c>
       <c r="D45" s="110" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="87">
-        <f>SUM(C44:C45)</f>
-        <v>179255</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="88"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="139">
+        <v>135031.6</v>
+      </c>
+      <c r="D46" s="110" t="str">
+        <f>D45</f>
+        <v>Debito 11/11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="139">
+        <v>272601.64</v>
+      </c>
+      <c r="D47" s="111" t="str">
+        <f>D46</f>
+        <v>Debito 11/11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="87">
+        <f>SUM(C44:C47)</f>
+        <v>1721186.6100000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="88"/>
+    </row>
+    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>137</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="139">
+        <v>538874.73</v>
+      </c>
+      <c r="D50" s="92" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="139">
+        <v>26232.46</v>
+      </c>
+      <c r="D51" s="111" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="139">
+        <v>675127.84</v>
+      </c>
+      <c r="D52" s="92" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="159" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="186">
-        <v>1298549.8600000001</v>
-      </c>
-      <c r="D48" s="110" t="s">
-        <v>154</v>
-      </c>
-      <c r="F48" s="128"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49" s="183">
-        <v>15003.51</v>
-      </c>
-      <c r="D49" s="110" t="s">
+      <c r="B53" s="160"/>
+      <c r="C53" s="139">
+        <v>177521</v>
+      </c>
+      <c r="D53" s="92" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="159" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="160"/>
+      <c r="C54" s="139">
+        <v>177521</v>
+      </c>
+      <c r="D54" s="92" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="150" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="151"/>
+      <c r="C55" s="139">
+        <v>100000</v>
+      </c>
+      <c r="D55" s="122" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" s="116"/>
+      <c r="C56" s="139">
+        <v>30600</v>
+      </c>
+      <c r="D56" s="122" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="87">
+        <f>SUM(C50:C56)</f>
+        <v>1725877.0299999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="18"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="90"/>
+    </row>
+    <row r="59" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="131" t="s">
+        <v>150</v>
+      </c>
+      <c r="B59" s="132"/>
+      <c r="C59" s="139">
+        <v>11200</v>
+      </c>
+      <c r="D59" s="133" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="B60" s="132"/>
+      <c r="C60" s="139">
+        <v>5600</v>
+      </c>
+      <c r="D60" s="133" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="150" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="151"/>
+      <c r="C61" s="139">
+        <f>135699+433009</f>
+        <v>568708</v>
+      </c>
+      <c r="D61" s="143" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="150" t="s">
+        <v>173</v>
+      </c>
+      <c r="B62" s="151"/>
+      <c r="C62" s="139">
+        <v>800000</v>
+      </c>
+      <c r="D62" s="143" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="144" t="s">
+        <v>177</v>
+      </c>
+      <c r="B63" s="145"/>
+      <c r="C63" s="139">
+        <v>116163</v>
+      </c>
+      <c r="D63" s="143" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="157" t="s">
+        <v>180</v>
+      </c>
+      <c r="B64" s="158"/>
+      <c r="C64" s="139">
+        <v>58500</v>
+      </c>
+      <c r="D64" s="143" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="107" t="s">
+        <v>167</v>
+      </c>
+      <c r="B65" s="146"/>
+      <c r="C65" s="139">
+        <v>85000</v>
+      </c>
+      <c r="D65" s="122" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="150" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" s="151"/>
+      <c r="C66" s="139">
+        <v>250000</v>
+      </c>
+      <c r="D66" s="122" t="s">
+        <v>161</v>
+      </c>
+      <c r="F66">
+        <f>7221852.61</f>
+        <v>7221852.6100000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="157" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C50" s="183">
-        <v>135031.6</v>
-      </c>
-      <c r="D50" s="110" t="str">
-        <f>D49</f>
-        <v>Debito 13/10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51" s="183">
-        <v>272601.64</v>
-      </c>
-      <c r="D51" s="111" t="str">
-        <f>D50</f>
-        <v>Debito 13/10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="87">
-        <f>SUM(C48:C51)</f>
-        <v>1721186.6100000003</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="88"/>
-    </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="B67" s="158"/>
+      <c r="C67" s="182">
+        <v>68800</v>
+      </c>
+      <c r="D67" s="122" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="27"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="94">
+        <f>SUM(C59:C67)</f>
+        <v>1963971</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="59"/>
+      <c r="C69" s="20"/>
+      <c r="D69" s="90"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="183">
-        <v>507167.57</v>
-      </c>
-      <c r="D54" s="138"/>
-    </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="183">
-        <v>26232.46</v>
-      </c>
-      <c r="D55" s="111" t="s">
-        <v>155</v>
-      </c>
-      <c r="F55">
-        <f>180000+82000</f>
-        <v>262000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="183">
-        <v>675127.84</v>
-      </c>
-      <c r="D56" s="92" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="158" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="159"/>
-      <c r="C57" s="183">
-        <v>177521</v>
-      </c>
-      <c r="D57" s="92" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B58" s="133"/>
-      <c r="C58" s="122">
-        <v>262000</v>
-      </c>
-      <c r="D58" s="122" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="116"/>
-      <c r="C59" s="183">
-        <v>30600</v>
-      </c>
-      <c r="D59" s="122" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="87">
-        <f>SUM(C54:C59)</f>
-        <v>1678648.87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="90"/>
-    </row>
-    <row r="62" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="132" t="s">
-        <v>151</v>
-      </c>
-      <c r="B62" s="133"/>
-      <c r="C62" s="141">
-        <v>11200</v>
-      </c>
-      <c r="D62" s="134" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="132" t="s">
-        <v>176</v>
-      </c>
-      <c r="B63" s="133"/>
-      <c r="C63" s="183">
-        <v>5600</v>
-      </c>
-      <c r="D63" s="145"/>
-    </row>
-    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="184"/>
-      <c r="B64" s="185"/>
-      <c r="C64" s="183">
-        <v>58500</v>
-      </c>
-      <c r="D64" s="145"/>
-    </row>
-    <row r="65" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="188" t="s">
-        <v>175</v>
-      </c>
-      <c r="B65" s="189"/>
-      <c r="C65" s="183">
-        <v>85000</v>
-      </c>
-      <c r="D65" s="122" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="151" t="s">
-        <v>174</v>
-      </c>
-      <c r="B66" s="152"/>
-      <c r="C66" s="183">
-        <v>250000</v>
-      </c>
-      <c r="D66" s="122" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="146" t="s">
-        <v>177</v>
-      </c>
-      <c r="B67" s="147"/>
-      <c r="C67" s="183">
-        <v>15000</v>
-      </c>
-      <c r="D67" s="122"/>
-    </row>
-    <row r="68" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="156" t="s">
-        <v>168</v>
-      </c>
-      <c r="B68" s="157"/>
-      <c r="C68" s="186">
-        <v>68800</v>
-      </c>
-      <c r="D68" s="122" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="94">
-        <f>SUM(C62:C68)</f>
-        <v>494100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="59"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="90"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="5"/>
+      <c r="C70" s="139">
+        <v>56820.35</v>
+      </c>
+      <c r="D70" s="95"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B71" s="5"/>
-      <c r="C71" s="141">
-        <v>56820.35</v>
-      </c>
-      <c r="D71" s="95"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="141">
-        <v>80545.34</v>
-      </c>
-      <c r="D72" s="93"/>
-    </row>
-    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="45" t="s">
+      <c r="C71" s="139">
+        <f>1040.56+1170+119411.66</f>
+        <v>121622.22</v>
+      </c>
+      <c r="D71" s="93"/>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B73" s="45"/>
-      <c r="C73" s="96"/>
-      <c r="D73" s="87">
-        <f>SUM(C71:C72)</f>
-        <v>137365.69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="97"/>
-    </row>
-    <row r="75" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="153" t="s">
-        <v>147</v>
-      </c>
-      <c r="B75" s="154"/>
-      <c r="C75" s="155"/>
-      <c r="D75" s="98">
-        <f>9000000-6763271.11-257950</f>
-        <v>1978778.8899999997</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="1"/>
-      <c r="C76" s="99"/>
-      <c r="D76" s="100"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="87">
+        <f>SUM(C70:C71)</f>
+        <v>178442.57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="97"/>
+    </row>
+    <row r="74" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="154" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="155"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="98">
+        <f>9000000-8119017.85</f>
+        <v>880982.15000000037</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="C75" s="99"/>
+      <c r="D75" s="100"/>
+      <c r="E75" s="40"/>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="101"/>
+      <c r="D76" s="102">
+        <f>(SUM(D28:D74))</f>
+        <v>9000000</v>
+      </c>
       <c r="E76" s="40"/>
     </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="10"/>
-      <c r="C77" s="101"/>
-      <c r="D77" s="102">
-        <f>(SUM(D29:D75))</f>
-        <v>9684742.6999999993</v>
-      </c>
-      <c r="E77" s="40"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C77" s="99"/>
+      <c r="D77" s="99"/>
+      <c r="F77" s="130"/>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C78" s="99"/>
       <c r="D78" s="99"/>
-      <c r="F78" s="131"/>
-    </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C79" s="99"/>
-      <c r="D79" s="99"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="12"/>
-      <c r="C80" s="103"/>
-      <c r="D80" s="104"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="151"/>
-      <c r="B81" s="152"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="103"/>
+      <c r="D79" s="104"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="150"/>
+      <c r="B80" s="151"/>
+      <c r="C80" s="91"/>
+      <c r="D80" s="89"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="150"/>
+      <c r="B81" s="151"/>
       <c r="C81" s="91"/>
       <c r="D81" s="89"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="151"/>
-      <c r="B82" s="152"/>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="107"/>
+      <c r="B82" s="108"/>
       <c r="C82" s="91"/>
       <c r="D82" s="89"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="107"/>
-      <c r="B83" s="108"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="89"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="43"/>
-      <c r="B84" s="42"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51">
-        <f>SUM(C81:C83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="21" t="s">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="43"/>
+      <c r="B83" s="42"/>
+      <c r="C83" s="51"/>
+      <c r="D83" s="51">
+        <f>SUM(C80:C82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="115"/>
-    </row>
-    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+      <c r="B86" s="21"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="115"/>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B89" s="10"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="61">
-        <f>D84+D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="10"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="61">
+        <f>D83+D86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="81" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" s="82">
+        <f>D76</f>
+        <v>9000000</v>
+      </c>
+      <c r="C90" s="40"/>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B91" s="82">
-        <f>D77</f>
-        <v>9684742.6999999993</v>
-      </c>
-      <c r="C91" s="40"/>
-    </row>
-    <row r="92" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>D76-D74</f>
+        <v>8119017.8499999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="81" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B92" s="82">
-        <f>D77-D75</f>
-        <v>7705963.8099999996</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>D88-D86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="81" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="B93" s="82">
-        <f>D89-D87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="81" t="s">
-        <v>88</v>
-      </c>
-      <c r="B94" s="82">
-        <f>D89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="150"/>
-      <c r="B97" s="150"/>
-      <c r="C97" s="150"/>
-      <c r="D97" s="150"/>
-    </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="150"/>
-      <c r="B98" s="150"/>
-      <c r="C98" s="150"/>
-      <c r="D98" s="150"/>
-    </row>
-    <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="150"/>
-      <c r="B99" s="150"/>
-      <c r="C99" s="150"/>
-      <c r="D99" s="150"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="15" t="s">
+        <f>D88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="163"/>
+      <c r="B96" s="163"/>
+      <c r="C96" s="163"/>
+      <c r="D96" s="163"/>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="163"/>
+      <c r="B97" s="163"/>
+      <c r="C97" s="163"/>
+      <c r="D97" s="163"/>
+    </row>
+    <row r="98" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="163"/>
+      <c r="B98" s="163"/>
+      <c r="C98" s="163"/>
+      <c r="D98" s="163"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B101" s="36"/>
-    </row>
-    <row r="102" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="24" t="s">
+      <c r="B100" s="36"/>
+    </row>
+    <row r="101" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B102" s="112">
-        <v>3268631.95</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="112">
+        <v>3705340.9299999988</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B102" s="37">
+        <f>PRORRATEO!H34</f>
+        <v>8734155.0999999996</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B103" s="37">
-        <f>PRORRATEO!H34</f>
-        <v>7623071.0899999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B104" s="93">
-        <f>B119</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B105" s="136">
-        <v>-46641</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="35" t="s">
+      <c r="B103" s="93">
+        <f>B118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="135"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="35" t="s">
         <v>44</v>
       </c>
+      <c r="B105" s="93">
+        <f>-B91</f>
+        <v>-8119017.8499999996</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>45</v>
+      </c>
       <c r="B106" s="93">
-        <f>-B92</f>
-        <v>-7705963.8099999996</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" s="93">
-        <f>-(B93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="23" t="s">
+        <f>-(B92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B108" s="112">
-        <f>SUM(B102:B107)</f>
-        <v>3139098.2299999995</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="38"/>
-      <c r="C109" s="40"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="149" t="s">
+      <c r="B107" s="112">
+        <f>SUM(B101:B106)</f>
+        <v>4320478.1799999978</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="38"/>
+      <c r="C108" s="40"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="162" t="s">
         <v>78</v>
       </c>
-      <c r="B111" s="149"/>
-    </row>
-    <row r="112" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="149"/>
-      <c r="B112" s="149"/>
-    </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="162"/>
+    </row>
+    <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="162"/>
+      <c r="B111" s="162"/>
+    </row>
+    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="105"/>
+      <c r="B112" s="30"/>
+    </row>
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="105"/>
       <c r="B113" s="30"/>
     </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="105"/>
       <c r="B114" s="30"/>
     </row>
-    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="105"/>
       <c r="B115" s="30"/>
     </row>
-    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="105"/>
       <c r="B116" s="30"/>
     </row>
-    <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="105"/>
-      <c r="B117" s="30"/>
-    </row>
-    <row r="118" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="105"/>
-      <c r="B118" s="129"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="41" t="s">
+      <c r="B117" s="128"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B119" s="106">
-        <f>SUM(B113:B118)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L120" s="8"/>
-    </row>
-    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="148"/>
-      <c r="B121" s="148"/>
-      <c r="C121" s="148"/>
-      <c r="D121" s="148"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="148"/>
-      <c r="B122" s="148"/>
-      <c r="C122" s="148"/>
-      <c r="D122" s="148"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="148"/>
-      <c r="B123" s="148"/>
-      <c r="C123" s="148"/>
-      <c r="D123" s="148"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="148"/>
-      <c r="B124" s="148"/>
-      <c r="C124" s="148"/>
-      <c r="D124" s="148"/>
+      <c r="B118" s="106">
+        <f>SUM(B112:B117)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L119" s="8"/>
+    </row>
+    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="161"/>
+      <c r="B120" s="161"/>
+      <c r="C120" s="161"/>
+      <c r="D120" s="161"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="161"/>
+      <c r="B121" s="161"/>
+      <c r="C121" s="161"/>
+      <c r="D121" s="161"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" s="161"/>
+      <c r="B122" s="161"/>
+      <c r="C122" s="161"/>
+      <c r="D122" s="161"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" s="161"/>
+      <c r="B123" s="161"/>
+      <c r="C123" s="161"/>
+      <c r="D123" s="161"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="F27:G28"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A57:B57"/>
+  <mergeCells count="20">
+    <mergeCell ref="A120:D123"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A96:D98"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A121:D124"/>
-    <mergeCell ref="A111:B112"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A14:D17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2907,84 +2924,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="14.109375" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="171" t="s">
-        <v>150</v>
-      </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
+      <c r="B1" s="164" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="164"/>
+      <c r="H1" s="164"/>
+      <c r="I1" s="164"/>
+      <c r="J1" s="164"/>
+      <c r="K1" s="164"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="130">
+      <c r="O2" s="129">
         <v>9000000</v>
       </c>
       <c r="P2" s="47"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="165"/>
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="165"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="165"/>
+      <c r="J3" s="165"/>
+      <c r="K3" s="165"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -2993,79 +3010,79 @@
       <c r="O3" s="48"/>
       <c r="P3" s="52"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="165" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="C4" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="169" t="s">
+      <c r="D4" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="169" t="s">
+      <c r="E4" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="169" t="s">
+      <c r="F4" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="G4" s="168" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="169" t="s">
+      <c r="H4" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="169" t="s">
+      <c r="I4" s="168" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="170" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="176" t="s">
+      <c r="L4" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="170" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="N4" s="176" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="173" t="s">
+      <c r="P4" s="166" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
-    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="166"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="182"/>
+    <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="179"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="174"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="177"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/12</v>
       </c>
-      <c r="P5" s="174"/>
-    </row>
-    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="167"/>
+    </row>
+    <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3083,19 +3100,20 @@
         <v>4.57</v>
       </c>
       <c r="G6" s="63">
-        <v>309800.01</v>
+        <v>421389.01</v>
       </c>
       <c r="H6" s="64">
-        <v>300000</v>
+        <f>G6</f>
+        <v>421389.01</v>
       </c>
       <c r="I6" s="65"/>
       <c r="J6" s="66">
         <f>G6-H6</f>
-        <v>9800.0100000000093</v>
+        <v>0</v>
       </c>
       <c r="K6" s="66">
         <f>IF(J6&gt;0,J6*2.95%,0)</f>
-        <v>289.1002950000003</v>
+        <v>0</v>
       </c>
       <c r="L6" s="67">
         <f>O$3*F6%</f>
@@ -3110,17 +3128,17 @@
       </c>
       <c r="O6" s="69">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>421389.01</v>
+        <v>411300.01</v>
       </c>
       <c r="P6" s="70">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>434031.01</v>
+        <v>423639.01</v>
       </c>
       <c r="Q6" s="40">
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -3138,19 +3156,17 @@
         <v>3.07</v>
       </c>
       <c r="G7" s="63">
-        <v>441287.02</v>
-      </c>
-      <c r="H7" s="64">
-        <v>214900</v>
-      </c>
+        <v>509365.02</v>
+      </c>
+      <c r="H7" s="64"/>
       <c r="I7" s="65"/>
       <c r="J7" s="66">
         <f t="shared" ref="J7:J31" si="2">G7-H7</f>
-        <v>226387.02000000002</v>
+        <v>509365.02</v>
       </c>
       <c r="K7" s="66">
         <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
-        <v>6678.4170900000008</v>
+        <v>15026.268090000001</v>
       </c>
       <c r="L7" s="67">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
@@ -3165,21 +3181,21 @@
       </c>
       <c r="O7" s="69">
         <f t="shared" si="0"/>
-        <v>509365.02</v>
+        <v>800691.02</v>
       </c>
       <c r="P7" s="70">
         <f t="shared" si="1"/>
-        <v>524646.02</v>
+        <v>824712.02</v>
       </c>
       <c r="Q7" s="40">
         <f>Q6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="R7" s="40" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3189,27 +3205,27 @@
       <c r="C8" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="137" t="s">
-        <v>149</v>
+      <c r="D8" s="136" t="s">
+        <v>148</v>
       </c>
       <c r="E8" s="57"/>
       <c r="F8" s="62">
         <v>4.55</v>
       </c>
       <c r="G8" s="63">
-        <v>2192843.0299999998</v>
+        <v>2339136.0299999998</v>
       </c>
       <c r="H8" s="64">
-        <v>318500</v>
+        <v>409500</v>
       </c>
       <c r="I8" s="65"/>
       <c r="J8" s="66">
         <f t="shared" si="2"/>
-        <v>1874343.0299999998</v>
+        <v>1929636.0299999998</v>
       </c>
       <c r="K8" s="66">
         <f t="shared" si="3"/>
-        <v>55293.119384999998</v>
+        <v>56924.262884999996</v>
       </c>
       <c r="L8" s="67">
         <f t="shared" si="4"/>
@@ -3224,18 +3240,18 @@
       </c>
       <c r="O8" s="69">
         <f t="shared" si="0"/>
-        <v>2339136.0299999998</v>
+        <v>2396060.0299999998</v>
       </c>
       <c r="P8" s="70">
         <f t="shared" si="1"/>
-        <v>2409310.0299999998</v>
+        <v>2467942.0299999998</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>14</v>
       </c>
@@ -3253,19 +3269,19 @@
         <v>3.05</v>
       </c>
       <c r="G9" s="63">
-        <v>191479.04000000001</v>
+        <v>253358.04</v>
       </c>
       <c r="H9" s="64">
-        <v>220000</v>
+        <v>210000</v>
       </c>
       <c r="I9" s="65"/>
       <c r="J9" s="66">
         <f t="shared" si="2"/>
-        <v>-28520.959999999992</v>
+        <v>43358.040000000008</v>
       </c>
       <c r="K9" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1279.0621800000004</v>
       </c>
       <c r="L9" s="67">
         <f t="shared" si="4"/>
@@ -3280,22 +3296,22 @@
       </c>
       <c r="O9" s="69">
         <f t="shared" si="0"/>
-        <v>245979.04</v>
+        <v>319137.03999999998</v>
       </c>
       <c r="P9" s="70">
         <f t="shared" si="1"/>
-        <v>253358.04</v>
+        <v>328711.03999999998</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="R9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S9" s="40"/>
     </row>
-    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3313,16 +3329,15 @@
         <v>4.55</v>
       </c>
       <c r="G10" s="63">
-        <v>316848.05</v>
+        <v>409348.05</v>
       </c>
       <c r="H10" s="64">
-        <f>127000+RESUMEN!C64+RESUMEN!C66</f>
-        <v>435500</v>
+        <v>410000</v>
       </c>
       <c r="I10" s="65"/>
       <c r="J10" s="66">
         <f t="shared" si="2"/>
-        <v>-118651.95000000001</v>
+        <v>-651.95000000001164</v>
       </c>
       <c r="K10" s="66">
         <f t="shared" si="3"/>
@@ -3341,11 +3356,11 @@
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>290848.05</v>
+        <v>408848.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>299573.05</v>
+        <v>421113.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3353,7 +3368,7 @@
       </c>
       <c r="S10" s="40"/>
     </row>
-    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -3371,15 +3386,16 @@
         <v>3.05</v>
       </c>
       <c r="G11" s="63">
-        <v>213500.06</v>
+        <v>268095.06</v>
       </c>
       <c r="H11" s="64">
-        <v>219905.06</v>
+        <f>G11</f>
+        <v>268095.06</v>
       </c>
       <c r="I11" s="65"/>
       <c r="J11" s="66">
         <f t="shared" si="2"/>
-        <v>-6405</v>
+        <v>0</v>
       </c>
       <c r="K11" s="66">
         <f t="shared" si="3"/>
@@ -3398,28 +3414,28 @@
       </c>
       <c r="O11" s="69">
         <f t="shared" si="0"/>
-        <v>268095.06</v>
+        <v>274500.06</v>
       </c>
       <c r="P11" s="70">
         <f t="shared" si="1"/>
-        <v>276138.06</v>
+        <v>282735.06</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="56">
         <v>7</v>
       </c>
-      <c r="C12" s="135" t="s">
+      <c r="C12" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="135" t="s">
+      <c r="D12" s="134" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="56"/>
@@ -3427,19 +3443,20 @@
         <v>4.55</v>
       </c>
       <c r="G12" s="63">
-        <v>318500.07</v>
+        <v>408000.07</v>
       </c>
       <c r="H12" s="64">
-        <v>320000</v>
+        <f>28000+380000</f>
+        <v>408000</v>
       </c>
       <c r="I12" s="65"/>
       <c r="J12" s="66">
         <f t="shared" si="2"/>
-        <v>-1499.929999999993</v>
+        <v>7.0000000006984919E-2</v>
       </c>
       <c r="K12" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.0650000002060552E-3</v>
       </c>
       <c r="L12" s="67">
         <f t="shared" si="4"/>
@@ -3454,20 +3471,20 @@
       </c>
       <c r="O12" s="69">
         <f t="shared" si="0"/>
-        <v>408000.07</v>
+        <v>409500.07</v>
       </c>
       <c r="P12" s="70">
         <f t="shared" si="1"/>
-        <v>420240.07</v>
+        <v>421785.07</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="R12" s="131"/>
-      <c r="S12" s="128"/>
-    </row>
-    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="130"/>
+      <c r="S12" s="127"/>
+    </row>
+    <row r="13" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3485,15 +3502,15 @@
         <v>3.05</v>
       </c>
       <c r="G13" s="63">
-        <v>213500.08</v>
+        <v>268695.08</v>
       </c>
       <c r="H13" s="64">
-        <v>219305.08</v>
+        <v>276756.08</v>
       </c>
       <c r="I13" s="65"/>
       <c r="J13" s="66">
         <f t="shared" si="2"/>
-        <v>-5805</v>
+        <v>-8061</v>
       </c>
       <c r="K13" s="66">
         <f t="shared" si="3"/>
@@ -3512,18 +3529,18 @@
       </c>
       <c r="O13" s="69">
         <f t="shared" si="0"/>
-        <v>268695.08</v>
+        <v>266439.08</v>
       </c>
       <c r="P13" s="70">
         <f t="shared" si="1"/>
-        <v>276756.08</v>
+        <v>274432.08</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
@@ -3541,16 +3558,15 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="G14" s="63">
-        <v>319200.09000000003</v>
-      </c>
-      <c r="H14" s="139">
-        <f>176000+80000+64000</f>
-        <v>320000</v>
+        <v>409600.09</v>
+      </c>
+      <c r="H14" s="137">
+        <v>410000</v>
       </c>
       <c r="I14" s="65"/>
       <c r="J14" s="66">
         <f t="shared" si="2"/>
-        <v>-799.90999999997439</v>
+        <v>-399.90999999997439</v>
       </c>
       <c r="K14" s="66">
         <f t="shared" si="3"/>
@@ -3569,21 +3585,21 @@
       </c>
       <c r="O14" s="69">
         <f t="shared" si="0"/>
-        <v>409600.09</v>
+        <v>410000.09</v>
       </c>
       <c r="P14" s="70">
         <f t="shared" si="1"/>
-        <v>421888.09</v>
+        <v>422300.09</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="R14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
@@ -3601,19 +3617,19 @@
         <v>3.05</v>
       </c>
       <c r="G15" s="63">
-        <v>438298.1</v>
+        <v>505930.1</v>
       </c>
       <c r="H15" s="64">
-        <v>213500</v>
+        <v>505500</v>
       </c>
       <c r="I15" s="65"/>
       <c r="J15" s="66">
         <f t="shared" si="2"/>
-        <v>224798.09999999998</v>
+        <v>430.09999999997672</v>
       </c>
       <c r="K15" s="66">
         <f t="shared" si="3"/>
-        <v>6631.5439499999993</v>
+        <v>12.687949999999313</v>
       </c>
       <c r="L15" s="67">
         <f t="shared" si="4"/>
@@ -3628,21 +3644,21 @@
       </c>
       <c r="O15" s="69">
         <f t="shared" si="0"/>
-        <v>505930.1</v>
+        <v>274943.09999999998</v>
       </c>
       <c r="P15" s="70">
         <f t="shared" si="1"/>
-        <v>521108.1</v>
+        <v>283191.09999999998</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="R15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -3660,11 +3676,11 @@
         <v>4.55</v>
       </c>
       <c r="G16" s="63">
-        <v>318500.11</v>
+        <v>409500.11</v>
       </c>
       <c r="H16" s="65">
         <f>G16</f>
-        <v>318500.11</v>
+        <v>409500.11</v>
       </c>
       <c r="I16" s="65"/>
       <c r="J16" s="66">
@@ -3699,7 +3715,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -3717,20 +3733,17 @@
         <v>3.05</v>
       </c>
       <c r="G17" s="63">
-        <v>212641.12</v>
-      </c>
-      <c r="H17" s="64">
-        <f>166000+46641</f>
-        <v>212641</v>
-      </c>
+        <v>274500.12</v>
+      </c>
+      <c r="H17" s="64"/>
       <c r="I17" s="65"/>
       <c r="J17" s="66">
         <f t="shared" si="2"/>
-        <v>0.11999999999534339</v>
+        <v>274500.12</v>
       </c>
       <c r="K17" s="66">
         <f t="shared" si="3"/>
-        <v>3.53999999986263E-3</v>
+        <v>8097.7535400000006</v>
       </c>
       <c r="L17" s="67">
         <f t="shared" si="4"/>
@@ -3745,18 +3758,18 @@
       </c>
       <c r="O17" s="69">
         <f t="shared" si="0"/>
-        <v>274500.12</v>
+        <v>557098.12</v>
       </c>
       <c r="P17" s="70">
         <f t="shared" si="1"/>
-        <v>282735.12</v>
+        <v>573811.12</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -3774,15 +3787,15 @@
         <v>4.55</v>
       </c>
       <c r="G18" s="63">
-        <v>308945.13</v>
+        <v>400232.13</v>
       </c>
       <c r="H18" s="65">
-        <v>318213.13</v>
+        <v>412239.13</v>
       </c>
       <c r="I18" s="65"/>
       <c r="J18" s="66">
         <f t="shared" si="2"/>
-        <v>-9268</v>
+        <v>-12007</v>
       </c>
       <c r="K18" s="66">
         <f t="shared" si="3"/>
@@ -3801,18 +3814,18 @@
       </c>
       <c r="O18" s="69">
         <f t="shared" si="0"/>
-        <v>400232.13</v>
+        <v>397493.13</v>
       </c>
       <c r="P18" s="70">
         <f t="shared" si="1"/>
-        <v>412239.13</v>
+        <v>409418.13</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
@@ -3830,15 +3843,16 @@
         <v>3.18</v>
       </c>
       <c r="G19" s="63">
-        <v>222600.14</v>
+        <v>279522.14</v>
       </c>
       <c r="H19" s="64">
-        <v>229278.14</v>
+        <f>272844+6678.14</f>
+        <v>279522.14</v>
       </c>
       <c r="I19" s="65"/>
       <c r="J19" s="66">
         <f t="shared" si="2"/>
-        <v>-6678</v>
+        <v>0</v>
       </c>
       <c r="K19" s="66">
         <f t="shared" si="3"/>
@@ -3857,18 +3871,18 @@
       </c>
       <c r="O19" s="69">
         <f t="shared" si="0"/>
-        <v>279522.14</v>
+        <v>286200.14</v>
       </c>
       <c r="P19" s="70">
         <f t="shared" si="1"/>
-        <v>287908.14</v>
+        <v>294786.14</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -3886,11 +3900,11 @@
         <v>4.55</v>
       </c>
       <c r="G20" s="63">
-        <v>318500.15000000002</v>
+        <v>409500.15</v>
       </c>
       <c r="H20" s="64">
         <f>G20</f>
-        <v>318500.15000000002</v>
+        <v>409500.15</v>
       </c>
       <c r="I20" s="65"/>
       <c r="J20" s="66">
@@ -3925,7 +3939,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3943,15 +3957,15 @@
         <v>3.17</v>
       </c>
       <c r="G21" s="63">
-        <v>221900.16</v>
+        <v>278200.15999999997</v>
       </c>
       <c r="H21" s="64">
-        <v>229000</v>
+        <v>287000</v>
       </c>
       <c r="I21" s="65"/>
       <c r="J21" s="66">
         <f t="shared" si="2"/>
-        <v>-7099.8399999999965</v>
+        <v>-8799.8400000000256</v>
       </c>
       <c r="K21" s="66">
         <f t="shared" si="3"/>
@@ -3970,22 +3984,22 @@
       </c>
       <c r="O21" s="69">
         <f t="shared" si="0"/>
-        <v>278200.15999999997</v>
+        <v>276500.15999999997</v>
       </c>
       <c r="P21" s="70">
         <f t="shared" si="1"/>
-        <v>286546.15999999997</v>
+        <v>284795.15999999997</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="R21" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="S21" s="39"/>
     </row>
-    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4003,11 +4017,11 @@
         <v>4.55</v>
       </c>
       <c r="G22" s="64">
-        <v>646396.17000000004</v>
+        <v>421785.17</v>
       </c>
       <c r="H22" s="64">
         <f>G22</f>
-        <v>646396.17000000004</v>
+        <v>421785.17</v>
       </c>
       <c r="I22" s="65"/>
       <c r="J22" s="66">
@@ -4042,7 +4056,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4060,16 +4074,15 @@
         <v>3.17</v>
       </c>
       <c r="G23" s="63">
-        <v>215570.18</v>
+        <v>285300.18</v>
       </c>
       <c r="H23" s="64">
-        <f>G23</f>
-        <v>215570.18</v>
+        <v>293859.18</v>
       </c>
       <c r="I23" s="65"/>
       <c r="J23" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8559</v>
       </c>
       <c r="K23" s="66">
         <f t="shared" si="3"/>
@@ -4088,18 +4101,18 @@
       </c>
       <c r="O23" s="69">
         <f t="shared" si="0"/>
-        <v>285300.18</v>
+        <v>276741.18</v>
       </c>
       <c r="P23" s="70">
         <f t="shared" si="1"/>
-        <v>293859.18</v>
+        <v>285043.18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
@@ -4117,11 +4130,11 @@
         <v>4.55</v>
       </c>
       <c r="G24" s="63">
-        <v>308945.19</v>
-      </c>
-      <c r="H24" s="140">
+        <v>409500.19</v>
+      </c>
+      <c r="H24" s="138">
         <f>G24</f>
-        <v>308945.19</v>
+        <v>409500.19</v>
       </c>
       <c r="I24" s="65"/>
       <c r="J24" s="66">
@@ -4156,7 +4169,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
@@ -4174,11 +4187,11 @@
         <v>3.17</v>
       </c>
       <c r="G25" s="64">
-        <v>226900.2</v>
+        <v>285300.2</v>
       </c>
       <c r="H25" s="64">
         <f>G25</f>
-        <v>226900.2</v>
+        <v>285300.2</v>
       </c>
       <c r="I25" s="65"/>
       <c r="J25" s="66">
@@ -4213,10 +4226,10 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="S25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
@@ -4234,11 +4247,11 @@
         <v>4.55</v>
       </c>
       <c r="G26" s="63">
-        <v>318500.21000000002</v>
+        <v>409500.21</v>
       </c>
       <c r="H26" s="65">
         <f>G26</f>
-        <v>318500.21000000002</v>
+        <v>409500.21</v>
       </c>
       <c r="I26" s="65"/>
       <c r="J26" s="66">
@@ -4273,7 +4286,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4291,7 +4304,7 @@
         <v>3.17</v>
       </c>
       <c r="G27" s="63">
-        <v>58990.22</v>
+        <v>-37579.78</v>
       </c>
       <c r="H27" s="64">
         <f>381870.22</f>
@@ -4300,7 +4313,7 @@
       <c r="I27" s="65"/>
       <c r="J27" s="66">
         <f t="shared" si="2"/>
-        <v>-322880</v>
+        <v>-419450</v>
       </c>
       <c r="K27" s="66">
         <f t="shared" si="3"/>
@@ -4319,18 +4332,18 @@
       </c>
       <c r="O27" s="69">
         <f t="shared" si="0"/>
-        <v>-37579.78</v>
+        <v>-134149.78</v>
       </c>
       <c r="P27" s="70">
         <f t="shared" si="1"/>
-        <v>-38706.78</v>
+        <v>-138173.78</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4348,11 +4361,11 @@
         <v>4.66</v>
       </c>
       <c r="G28" s="63">
-        <v>325906.23</v>
+        <v>419400.23</v>
       </c>
       <c r="H28" s="65">
         <f>G28</f>
-        <v>325906.23</v>
+        <v>419400.23</v>
       </c>
       <c r="I28" s="65"/>
       <c r="J28" s="66">
@@ -4387,7 +4400,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4405,11 +4418,11 @@
         <v>3.21</v>
       </c>
       <c r="G29" s="63">
-        <v>224700.24</v>
+        <v>288900.24</v>
       </c>
       <c r="H29" s="65">
         <f>G29</f>
-        <v>224700.24</v>
+        <v>288900.24</v>
       </c>
       <c r="I29" s="65"/>
       <c r="J29" s="66">
@@ -4444,7 +4457,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>27</v>
       </c>
@@ -4462,15 +4475,16 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="G30" s="63">
-        <v>328300.25</v>
+        <v>412251.25</v>
       </c>
       <c r="H30" s="65">
-        <v>338149.25</v>
+        <f>G30</f>
+        <v>412251.25</v>
       </c>
       <c r="I30" s="65"/>
       <c r="J30" s="66">
         <f t="shared" si="2"/>
-        <v>-9849</v>
+        <v>0</v>
       </c>
       <c r="K30" s="66">
         <f t="shared" si="3"/>
@@ -4489,21 +4503,21 @@
       </c>
       <c r="O30" s="69">
         <f t="shared" si="0"/>
-        <v>412251.25</v>
+        <v>422100.25</v>
       </c>
       <c r="P30" s="70">
         <f t="shared" si="1"/>
-        <v>424619.25</v>
+        <v>434763.25</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
       <c r="R30" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
@@ -4521,16 +4535,15 @@
         <v>3.02</v>
       </c>
       <c r="G31" s="63">
-        <v>217742.26</v>
+        <v>271800.26</v>
       </c>
       <c r="H31" s="65">
-        <f>G31</f>
-        <v>217742.26</v>
+        <v>279954.26</v>
       </c>
       <c r="I31" s="65"/>
       <c r="J31" s="66">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-8154</v>
       </c>
       <c r="K31" s="66">
         <f t="shared" si="3"/>
@@ -4549,22 +4562,22 @@
       </c>
       <c r="O31" s="69">
         <f t="shared" si="0"/>
-        <v>271800.26</v>
+        <v>263646.26</v>
       </c>
       <c r="P31" s="70">
         <f t="shared" si="1"/>
-        <v>279954.26</v>
+        <v>271555.26</v>
       </c>
       <c r="Q31" s="121">
         <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="128"/>
+      <c r="R31" s="127"/>
       <c r="S31" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>27</v>
       </c>
@@ -4582,16 +4595,15 @@
         <v>0.16</v>
       </c>
       <c r="G32" s="63">
-        <v>10648.27</v>
+        <v>14400.27</v>
       </c>
       <c r="H32" s="65">
-        <f>G32</f>
-        <v>10648.27</v>
+        <v>14832.27</v>
       </c>
       <c r="I32" s="65"/>
       <c r="J32" s="66">
         <f>G32-H32</f>
-        <v>0</v>
+        <v>-432</v>
       </c>
       <c r="K32" s="66">
         <f t="shared" si="3"/>
@@ -4610,18 +4622,18 @@
       </c>
       <c r="O32" s="69">
         <f t="shared" si="0"/>
-        <v>14400.27</v>
+        <v>13968.27</v>
       </c>
       <c r="P32" s="70">
         <f t="shared" si="1"/>
-        <v>14832.27</v>
+        <v>14387.27</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
@@ -4667,7 +4679,7 @@
       </c>
       <c r="Q33" s="40"/>
     </row>
-    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="76"/>
       <c r="C34" s="77"/>
       <c r="D34" s="78"/>
@@ -4678,11 +4690,11 @@
       </c>
       <c r="G34" s="46">
         <f>SUM(G6:G33)</f>
-        <v>9440941.7799999993</v>
+        <v>11024929.779999999</v>
       </c>
       <c r="H34" s="54">
         <f>SUM(H6:H33)</f>
-        <v>7623071.0899999999</v>
+        <v>8734155.0999999996</v>
       </c>
       <c r="I34" s="54">
         <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
@@ -4704,106 +4716,111 @@
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>10886765.779999999</v>
+        <v>11372117.779999999</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>11213369.779999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11713280.779999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D37" s="148" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
-      <c r="H37" s="148"/>
-      <c r="I37" s="148"/>
-      <c r="J37" s="148"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="148"/>
-      <c r="M37" s="148"/>
-      <c r="N37" s="148"/>
-      <c r="O37" s="148"/>
-    </row>
-    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="148"/>
-      <c r="E38" s="148"/>
-      <c r="F38" s="148"/>
-      <c r="G38" s="148"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="148"/>
-      <c r="J38" s="148"/>
-      <c r="K38" s="148"/>
-      <c r="L38" s="148"/>
-      <c r="M38" s="148"/>
-      <c r="N38" s="148"/>
-      <c r="O38" s="148"/>
-    </row>
-    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="148"/>
-      <c r="E39" s="148"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="148"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="148"/>
-      <c r="L39" s="148"/>
-      <c r="M39" s="148"/>
-      <c r="N39" s="148"/>
-      <c r="O39" s="148"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="148"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="148"/>
-      <c r="H40" s="148"/>
-      <c r="I40" s="148"/>
-      <c r="J40" s="148"/>
-      <c r="K40" s="148"/>
-      <c r="L40" s="148"/>
-      <c r="M40" s="148"/>
-      <c r="N40" s="148"/>
-      <c r="O40" s="148"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D41" s="148"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="148"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="148"/>
-      <c r="N41" s="148"/>
-      <c r="O41" s="148"/>
-    </row>
-    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
-      <c r="H42" s="148"/>
-      <c r="I42" s="148"/>
-      <c r="J42" s="148"/>
-      <c r="K42" s="148"/>
-      <c r="L42" s="148"/>
-      <c r="M42" s="148"/>
-      <c r="N42" s="148"/>
-      <c r="O42" s="148"/>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="161" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" s="161"/>
+      <c r="F37" s="161"/>
+      <c r="G37" s="161"/>
+      <c r="H37" s="161"/>
+      <c r="I37" s="161"/>
+      <c r="J37" s="161"/>
+      <c r="K37" s="161"/>
+      <c r="L37" s="161"/>
+      <c r="M37" s="161"/>
+      <c r="N37" s="161"/>
+      <c r="O37" s="161"/>
+    </row>
+    <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="161"/>
+      <c r="E38" s="161"/>
+      <c r="F38" s="161"/>
+      <c r="G38" s="161"/>
+      <c r="H38" s="161"/>
+      <c r="I38" s="161"/>
+      <c r="J38" s="161"/>
+      <c r="K38" s="161"/>
+      <c r="L38" s="161"/>
+      <c r="M38" s="161"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="161"/>
+    </row>
+    <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="161"/>
+      <c r="E39" s="161"/>
+      <c r="F39" s="161"/>
+      <c r="G39" s="161"/>
+      <c r="H39" s="161"/>
+      <c r="I39" s="161"/>
+      <c r="J39" s="161"/>
+      <c r="K39" s="161"/>
+      <c r="L39" s="161"/>
+      <c r="M39" s="161"/>
+      <c r="N39" s="161"/>
+      <c r="O39" s="161"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="161"/>
+      <c r="E40" s="161"/>
+      <c r="F40" s="161"/>
+      <c r="G40" s="161"/>
+      <c r="H40" s="161"/>
+      <c r="I40" s="161"/>
+      <c r="J40" s="161"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="161"/>
+      <c r="M40" s="161"/>
+      <c r="N40" s="161"/>
+      <c r="O40" s="161"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="161"/>
+      <c r="E41" s="161"/>
+      <c r="F41" s="161"/>
+      <c r="G41" s="161"/>
+      <c r="H41" s="161"/>
+      <c r="I41" s="161"/>
+      <c r="J41" s="161"/>
+      <c r="K41" s="161"/>
+      <c r="L41" s="161"/>
+      <c r="M41" s="161"/>
+      <c r="N41" s="161"/>
+      <c r="O41" s="161"/>
+    </row>
+    <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="161"/>
+      <c r="E42" s="161"/>
+      <c r="F42" s="161"/>
+      <c r="G42" s="161"/>
+      <c r="H42" s="161"/>
+      <c r="I42" s="161"/>
+      <c r="J42" s="161"/>
+      <c r="K42" s="161"/>
+      <c r="L42" s="161"/>
+      <c r="M42" s="161"/>
+      <c r="N42" s="161"/>
+      <c r="O42" s="161"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4816,11 +4833,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
+++ b/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AE1835-07CF-44A6-85DB-AA8BBB0E2CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0D6E23-21CC-4C33-8905-5B3BE48FF4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1435,6 +1435,43 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1444,47 +1481,29 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1498,9 +1517,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1510,9 +1526,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1528,19 +1541,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1933,68 +1933,68 @@
       <c r="D3" s="119"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="163" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="152"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="152"/>
-      <c r="B5" s="152"/>
+      <c r="A5" s="163"/>
+      <c r="B5" s="163"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="152"/>
-      <c r="B6" s="152"/>
+      <c r="A6" s="163"/>
+      <c r="B6" s="163"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="152"/>
-      <c r="B7" s="152"/>
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="149" t="s">
+      <c r="B9" s="162" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="149"/>
+      <c r="B10" s="162"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="149"/>
+      <c r="B11" s="162"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="164" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="153"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="153"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="164"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="153"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
+      <c r="A15" s="164"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="153"/>
-      <c r="B16" s="153"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="153"/>
+      <c r="A16" s="164"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="164"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="153"/>
-      <c r="B17" s="153"/>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
+      <c r="A17" s="164"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="164"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2068,10 +2068,10 @@
         <v>1008674.64</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="147" t="s">
+      <c r="F27" s="160" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="148"/>
+      <c r="G27" s="161"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -2207,10 +2207,10 @@
       <c r="D39" s="60"/>
     </row>
     <row r="40" spans="1:7" s="34" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="150" t="s">
+      <c r="A40" s="151" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="151"/>
+      <c r="B40" s="152"/>
       <c r="C40" s="140">
         <v>175052</v>
       </c>
@@ -2219,10 +2219,10 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="150" t="s">
+      <c r="A41" s="151" t="s">
         <v>129</v>
       </c>
-      <c r="B41" s="151"/>
+      <c r="B41" s="152"/>
       <c r="C41" s="141">
         <v>4203</v>
       </c>
@@ -2256,7 +2256,7 @@
       <c r="B44" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C44" s="182">
+      <c r="C44" s="147">
         <v>1298549.8600000001</v>
       </c>
       <c r="D44" s="110" t="s">
@@ -2364,10 +2364,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="159" t="s">
+      <c r="A53" s="158" t="s">
         <v>169</v>
       </c>
-      <c r="B53" s="160"/>
+      <c r="B53" s="159"/>
       <c r="C53" s="139">
         <v>177521</v>
       </c>
@@ -2376,10 +2376,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="159" t="s">
+      <c r="A54" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="B54" s="160"/>
+      <c r="B54" s="159"/>
       <c r="C54" s="139">
         <v>177521</v>
       </c>
@@ -2388,10 +2388,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="150" t="s">
+      <c r="A55" s="151" t="s">
         <v>178</v>
       </c>
-      <c r="B55" s="151"/>
+      <c r="B55" s="152"/>
       <c r="C55" s="139">
         <v>100000</v>
       </c>
@@ -2455,10 +2455,10 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="150" t="s">
+      <c r="A61" s="151" t="s">
         <v>171</v>
       </c>
-      <c r="B61" s="151"/>
+      <c r="B61" s="152"/>
       <c r="C61" s="139">
         <f>135699+433009</f>
         <v>568708</v>
@@ -2468,10 +2468,10 @@
       </c>
     </row>
     <row r="62" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="150" t="s">
+      <c r="A62" s="151" t="s">
         <v>173</v>
       </c>
-      <c r="B62" s="151"/>
+      <c r="B62" s="152"/>
       <c r="C62" s="139">
         <v>800000</v>
       </c>
@@ -2492,10 +2492,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="157" t="s">
+      <c r="A64" s="156" t="s">
         <v>180</v>
       </c>
-      <c r="B64" s="158"/>
+      <c r="B64" s="157"/>
       <c r="C64" s="139">
         <v>58500</v>
       </c>
@@ -2516,10 +2516,10 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="150" t="s">
+      <c r="A66" s="151" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="151"/>
+      <c r="B66" s="152"/>
       <c r="C66" s="139">
         <v>250000</v>
       </c>
@@ -2532,11 +2532,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="157" t="s">
+      <c r="A67" s="156" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="158"/>
-      <c r="C67" s="182">
+      <c r="B67" s="157"/>
+      <c r="C67" s="147">
         <v>68800</v>
       </c>
       <c r="D67" s="122" t="s">
@@ -2601,11 +2601,11 @@
       <c r="D73" s="97"/>
     </row>
     <row r="74" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="154" t="s">
+      <c r="A74" s="153" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="155"/>
-      <c r="C74" s="156"/>
+      <c r="B74" s="154"/>
+      <c r="C74" s="155"/>
       <c r="D74" s="98">
         <f>9000000-8119017.85</f>
         <v>880982.15000000037</v>
@@ -2647,14 +2647,14 @@
       <c r="D79" s="104"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="150"/>
-      <c r="B80" s="151"/>
+      <c r="A80" s="151"/>
+      <c r="B80" s="152"/>
       <c r="C80" s="91"/>
       <c r="D80" s="89"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="150"/>
-      <c r="B81" s="151"/>
+      <c r="A81" s="151"/>
+      <c r="B81" s="152"/>
       <c r="C81" s="91"/>
       <c r="D81" s="89"/>
     </row>
@@ -2681,7 +2681,9 @@
       </c>
       <c r="B86" s="21"/>
       <c r="C86" s="22"/>
-      <c r="D86" s="115"/>
+      <c r="D86" s="115">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2692,7 +2694,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="61">
         <f>D83+D86</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2730,28 +2732,28 @@
       </c>
       <c r="B93" s="82">
         <f>D88</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="163"/>
-      <c r="B96" s="163"/>
-      <c r="C96" s="163"/>
-      <c r="D96" s="163"/>
+      <c r="A96" s="150"/>
+      <c r="B96" s="150"/>
+      <c r="C96" s="150"/>
+      <c r="D96" s="150"/>
     </row>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="163"/>
-      <c r="B97" s="163"/>
-      <c r="C97" s="163"/>
-      <c r="D97" s="163"/>
+      <c r="A97" s="150"/>
+      <c r="B97" s="150"/>
+      <c r="C97" s="150"/>
+      <c r="D97" s="150"/>
     </row>
     <row r="98" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="163"/>
-      <c r="B98" s="163"/>
-      <c r="C98" s="163"/>
-      <c r="D98" s="163"/>
+      <c r="A98" s="150"/>
+      <c r="B98" s="150"/>
+      <c r="C98" s="150"/>
+      <c r="D98" s="150"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
@@ -2823,14 +2825,14 @@
       <c r="C108" s="40"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="162" t="s">
+      <c r="A110" s="149" t="s">
         <v>78</v>
       </c>
-      <c r="B110" s="162"/>
+      <c r="B110" s="149"/>
     </row>
     <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="162"/>
-      <c r="B111" s="162"/>
+      <c r="A111" s="149"/>
+      <c r="B111" s="149"/>
     </row>
     <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="105"/>
@@ -2869,36 +2871,37 @@
       <c r="L119" s="8"/>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="161"/>
-      <c r="B120" s="161"/>
-      <c r="C120" s="161"/>
-      <c r="D120" s="161"/>
+      <c r="A120" s="148"/>
+      <c r="B120" s="148"/>
+      <c r="C120" s="148"/>
+      <c r="D120" s="148"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="161"/>
-      <c r="B121" s="161"/>
-      <c r="C121" s="161"/>
-      <c r="D121" s="161"/>
+      <c r="A121" s="148"/>
+      <c r="B121" s="148"/>
+      <c r="C121" s="148"/>
+      <c r="D121" s="148"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="161"/>
-      <c r="B122" s="161"/>
-      <c r="C122" s="161"/>
-      <c r="D122" s="161"/>
+      <c r="A122" s="148"/>
+      <c r="B122" s="148"/>
+      <c r="C122" s="148"/>
+      <c r="D122" s="148"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="161"/>
-      <c r="B123" s="161"/>
-      <c r="C123" s="161"/>
-      <c r="D123" s="161"/>
+      <c r="A123" s="148"/>
+      <c r="B123" s="148"/>
+      <c r="C123" s="148"/>
+      <c r="D123" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A120:D123"/>
-    <mergeCell ref="A110:B111"/>
-    <mergeCell ref="A96:D98"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A14:D17"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A53:B53"/>
@@ -2908,12 +2911,11 @@
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A120:D123"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A96:D98"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2949,18 +2951,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="164" t="s">
+      <c r="B1" s="171" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2969,16 +2971,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="164"/>
-      <c r="I2" s="164"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="171"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="171"/>
+      <c r="J2" s="171"/>
+      <c r="K2" s="171"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2992,95 +2994,97 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="165"/>
-      <c r="I3" s="165"/>
-      <c r="J3" s="165"/>
-      <c r="K3" s="165"/>
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="48"/>
+      <c r="O3" s="48">
+        <v>1000000</v>
+      </c>
       <c r="P3" s="52"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="178" t="s">
+      <c r="A4" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="167" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="168" t="s">
+      <c r="C4" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="168" t="s">
+      <c r="D4" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="169" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="168" t="s">
+      <c r="F4" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="168" t="s">
+      <c r="H4" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="168" t="s">
+      <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="173" t="s">
+      <c r="J4" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="170" t="s">
+      <c r="K4" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="170" t="s">
+      <c r="L4" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="170" t="s">
+      <c r="M4" s="176" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="176" t="s">
+      <c r="N4" s="181" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="166" t="s">
+      <c r="P4" s="173" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="179"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="174"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="175"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="177"/>
+      <c r="A5" s="166"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="180"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="182"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/12</v>
       </c>
-      <c r="P5" s="167"/>
+      <c r="P5" s="174"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3117,7 +3121,7 @@
       </c>
       <c r="L6" s="67">
         <f>O$3*F6%</f>
-        <v>0</v>
+        <v>45700.000000000007</v>
       </c>
       <c r="M6" s="67">
         <f>O$2*F6%</f>
@@ -3128,11 +3132,11 @@
       </c>
       <c r="O6" s="69">
         <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>411300.01</v>
+        <v>457000.01</v>
       </c>
       <c r="P6" s="70">
         <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
-        <v>423639.01</v>
+        <v>470710.01</v>
       </c>
       <c r="Q6" s="40">
         <v>0.01</v>
@@ -3170,7 +3174,7 @@
       </c>
       <c r="L7" s="67">
         <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
-        <v>0</v>
+        <v>30699.999999999996</v>
       </c>
       <c r="M7" s="67">
         <f t="shared" ref="M7:M33" si="5">O$2*F7%</f>
@@ -3181,11 +3185,11 @@
       </c>
       <c r="O7" s="69">
         <f t="shared" si="0"/>
-        <v>800691.02</v>
+        <v>831391.02</v>
       </c>
       <c r="P7" s="70">
         <f t="shared" si="1"/>
-        <v>824712.02</v>
+        <v>856333.02</v>
       </c>
       <c r="Q7" s="40">
         <f>Q6+0.01</f>
@@ -3229,7 +3233,7 @@
       </c>
       <c r="L8" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M8" s="67">
         <f t="shared" si="5"/>
@@ -3240,11 +3244,11 @@
       </c>
       <c r="O8" s="69">
         <f t="shared" si="0"/>
-        <v>2396060.0299999998</v>
+        <v>2441560.0299999998</v>
       </c>
       <c r="P8" s="70">
         <f t="shared" si="1"/>
-        <v>2467942.0299999998</v>
+        <v>2514807.0299999998</v>
       </c>
       <c r="Q8" s="40">
         <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
@@ -3285,7 +3289,7 @@
       </c>
       <c r="L9" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="M9" s="67">
         <f t="shared" si="5"/>
@@ -3296,11 +3300,11 @@
       </c>
       <c r="O9" s="69">
         <f t="shared" si="0"/>
-        <v>319137.03999999998</v>
+        <v>349637.04</v>
       </c>
       <c r="P9" s="70">
         <f t="shared" si="1"/>
-        <v>328711.03999999998</v>
+        <v>360126.04</v>
       </c>
       <c r="Q9" s="40">
         <f t="shared" si="6"/>
@@ -3345,7 +3349,7 @@
       </c>
       <c r="L10" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M10" s="67">
         <f t="shared" si="5"/>
@@ -3356,11 +3360,11 @@
       </c>
       <c r="O10" s="69">
         <f t="shared" si="0"/>
-        <v>408848.05</v>
+        <v>454348.05</v>
       </c>
       <c r="P10" s="70">
         <f t="shared" si="1"/>
-        <v>421113.05</v>
+        <v>467978.05</v>
       </c>
       <c r="Q10" s="40">
         <f t="shared" si="6"/>
@@ -3403,7 +3407,7 @@
       </c>
       <c r="L11" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="M11" s="67">
         <f t="shared" si="5"/>
@@ -3414,11 +3418,11 @@
       </c>
       <c r="O11" s="69">
         <f t="shared" si="0"/>
-        <v>274500.06</v>
+        <v>305000.06</v>
       </c>
       <c r="P11" s="70">
         <f t="shared" si="1"/>
-        <v>282735.06</v>
+        <v>314150.06</v>
       </c>
       <c r="Q11" s="40">
         <f t="shared" si="6"/>
@@ -3460,7 +3464,7 @@
       </c>
       <c r="L12" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M12" s="67">
         <f t="shared" si="5"/>
@@ -3471,11 +3475,11 @@
       </c>
       <c r="O12" s="69">
         <f t="shared" si="0"/>
-        <v>409500.07</v>
+        <v>455000.07</v>
       </c>
       <c r="P12" s="70">
         <f t="shared" si="1"/>
-        <v>421785.07</v>
+        <v>468650.07</v>
       </c>
       <c r="Q12" s="40">
         <f t="shared" si="6"/>
@@ -3518,7 +3522,7 @@
       </c>
       <c r="L13" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="M13" s="67">
         <f t="shared" si="5"/>
@@ -3529,11 +3533,11 @@
       </c>
       <c r="O13" s="69">
         <f t="shared" si="0"/>
-        <v>266439.08</v>
+        <v>296939.08</v>
       </c>
       <c r="P13" s="70">
         <f t="shared" si="1"/>
-        <v>274432.08</v>
+        <v>305847.08</v>
       </c>
       <c r="Q13" s="40">
         <f t="shared" si="6"/>
@@ -3574,7 +3578,7 @@
       </c>
       <c r="L14" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45599.999999999993</v>
       </c>
       <c r="M14" s="67">
         <f t="shared" si="5"/>
@@ -3585,11 +3589,11 @@
       </c>
       <c r="O14" s="69">
         <f t="shared" si="0"/>
-        <v>410000.09</v>
+        <v>455600.09</v>
       </c>
       <c r="P14" s="70">
         <f t="shared" si="1"/>
-        <v>422300.09</v>
+        <v>469268.09</v>
       </c>
       <c r="Q14" s="40">
         <f t="shared" si="6"/>
@@ -3633,7 +3637,7 @@
       </c>
       <c r="L15" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="M15" s="67">
         <f t="shared" si="5"/>
@@ -3644,11 +3648,11 @@
       </c>
       <c r="O15" s="69">
         <f t="shared" si="0"/>
-        <v>274943.09999999998</v>
+        <v>305443.09999999998</v>
       </c>
       <c r="P15" s="70">
         <f t="shared" si="1"/>
-        <v>283191.09999999998</v>
+        <v>314606.09999999998</v>
       </c>
       <c r="Q15" s="40">
         <f t="shared" si="6"/>
@@ -3693,7 +3697,7 @@
       </c>
       <c r="L16" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M16" s="67">
         <f t="shared" si="5"/>
@@ -3704,11 +3708,11 @@
       </c>
       <c r="O16" s="69">
         <f t="shared" si="0"/>
-        <v>409500.11</v>
+        <v>455000.11</v>
       </c>
       <c r="P16" s="70">
         <f t="shared" si="1"/>
-        <v>421785.11</v>
+        <v>468650.11</v>
       </c>
       <c r="Q16" s="40">
         <f t="shared" si="6"/>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="L17" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="M17" s="67">
         <f t="shared" si="5"/>
@@ -3758,11 +3762,11 @@
       </c>
       <c r="O17" s="69">
         <f t="shared" si="0"/>
-        <v>557098.12</v>
+        <v>587598.12</v>
       </c>
       <c r="P17" s="70">
         <f t="shared" si="1"/>
-        <v>573811.12</v>
+        <v>605226.12</v>
       </c>
       <c r="Q17" s="40">
         <f t="shared" si="6"/>
@@ -3803,7 +3807,7 @@
       </c>
       <c r="L18" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M18" s="67">
         <f t="shared" si="5"/>
@@ -3814,11 +3818,11 @@
       </c>
       <c r="O18" s="69">
         <f t="shared" si="0"/>
-        <v>397493.13</v>
+        <v>442993.13</v>
       </c>
       <c r="P18" s="70">
         <f t="shared" si="1"/>
-        <v>409418.13</v>
+        <v>456283.13</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" si="6"/>
@@ -3860,7 +3864,7 @@
       </c>
       <c r="L19" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31800.000000000004</v>
       </c>
       <c r="M19" s="67">
         <f t="shared" si="5"/>
@@ -3871,11 +3875,11 @@
       </c>
       <c r="O19" s="69">
         <f t="shared" si="0"/>
-        <v>286200.14</v>
+        <v>318000.14</v>
       </c>
       <c r="P19" s="70">
         <f t="shared" si="1"/>
-        <v>294786.14</v>
+        <v>327540.14</v>
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="6"/>
@@ -3917,7 +3921,7 @@
       </c>
       <c r="L20" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M20" s="67">
         <f t="shared" si="5"/>
@@ -3928,11 +3932,11 @@
       </c>
       <c r="O20" s="69">
         <f t="shared" si="0"/>
-        <v>409500.15</v>
+        <v>455000.15</v>
       </c>
       <c r="P20" s="70">
         <f t="shared" si="1"/>
-        <v>421785.15</v>
+        <v>468650.15</v>
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="6"/>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="L21" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="M21" s="67">
         <f t="shared" si="5"/>
@@ -3984,11 +3988,11 @@
       </c>
       <c r="O21" s="69">
         <f t="shared" si="0"/>
-        <v>276500.15999999997</v>
+        <v>308200.15999999997</v>
       </c>
       <c r="P21" s="70">
         <f t="shared" si="1"/>
-        <v>284795.15999999997</v>
+        <v>317446.15999999997</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" si="6"/>
@@ -4034,7 +4038,7 @@
       </c>
       <c r="L22" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M22" s="67">
         <f t="shared" si="5"/>
@@ -4045,11 +4049,11 @@
       </c>
       <c r="O22" s="69">
         <f t="shared" si="0"/>
-        <v>409500.17</v>
+        <v>455000.17</v>
       </c>
       <c r="P22" s="70">
         <f t="shared" si="1"/>
-        <v>421785.17</v>
+        <v>468650.17</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="6"/>
@@ -4090,7 +4094,7 @@
       </c>
       <c r="L23" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="M23" s="67">
         <f t="shared" si="5"/>
@@ -4101,11 +4105,11 @@
       </c>
       <c r="O23" s="69">
         <f t="shared" si="0"/>
-        <v>276741.18</v>
+        <v>308441.18</v>
       </c>
       <c r="P23" s="70">
         <f t="shared" si="1"/>
-        <v>285043.18</v>
+        <v>317694.18</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="6"/>
@@ -4147,7 +4151,7 @@
       </c>
       <c r="L24" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M24" s="67">
         <f t="shared" si="5"/>
@@ -4158,11 +4162,11 @@
       </c>
       <c r="O24" s="69">
         <f t="shared" si="0"/>
-        <v>409500.19</v>
+        <v>455000.19</v>
       </c>
       <c r="P24" s="70">
         <f t="shared" si="1"/>
-        <v>421785.19</v>
+        <v>468650.19</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" si="6"/>
@@ -4204,7 +4208,7 @@
       </c>
       <c r="L25" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="M25" s="67">
         <f t="shared" si="5"/>
@@ -4215,11 +4219,11 @@
       </c>
       <c r="O25" s="69">
         <f t="shared" si="0"/>
-        <v>285300.2</v>
+        <v>317000.2</v>
       </c>
       <c r="P25" s="70">
         <f t="shared" si="1"/>
-        <v>293859.20000000001</v>
+        <v>326510.2</v>
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="6"/>
@@ -4264,7 +4268,7 @@
       </c>
       <c r="L26" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45500</v>
       </c>
       <c r="M26" s="67">
         <f t="shared" si="5"/>
@@ -4275,11 +4279,11 @@
       </c>
       <c r="O26" s="69">
         <f t="shared" si="0"/>
-        <v>409500.21</v>
+        <v>455000.21</v>
       </c>
       <c r="P26" s="70">
         <f t="shared" si="1"/>
-        <v>421785.21</v>
+        <v>468650.21</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="6"/>
@@ -4321,7 +4325,7 @@
       </c>
       <c r="L27" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>31700</v>
       </c>
       <c r="M27" s="67">
         <f t="shared" si="5"/>
@@ -4332,11 +4336,11 @@
       </c>
       <c r="O27" s="69">
         <f t="shared" si="0"/>
-        <v>-134149.78</v>
+        <v>-102449.78</v>
       </c>
       <c r="P27" s="70">
         <f t="shared" si="1"/>
-        <v>-138173.78</v>
+        <v>-105522.78</v>
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="6"/>
@@ -4378,7 +4382,7 @@
       </c>
       <c r="L28" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46600</v>
       </c>
       <c r="M28" s="67">
         <f t="shared" si="5"/>
@@ -4389,11 +4393,11 @@
       </c>
       <c r="O28" s="69">
         <f t="shared" si="0"/>
-        <v>419400.23</v>
+        <v>466000.23</v>
       </c>
       <c r="P28" s="70">
         <f t="shared" si="1"/>
-        <v>431982.23</v>
+        <v>479980.23</v>
       </c>
       <c r="Q28" s="40">
         <f t="shared" si="6"/>
@@ -4435,7 +4439,7 @@
       </c>
       <c r="L29" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>32099.999999999996</v>
       </c>
       <c r="M29" s="67">
         <f t="shared" si="5"/>
@@ -4446,11 +4450,11 @@
       </c>
       <c r="O29" s="69">
         <f t="shared" si="0"/>
-        <v>288900.24</v>
+        <v>321000.24</v>
       </c>
       <c r="P29" s="70">
         <f t="shared" si="1"/>
-        <v>297567.24</v>
+        <v>330630.24</v>
       </c>
       <c r="Q29" s="40">
         <f t="shared" si="6"/>
@@ -4492,7 +4496,7 @@
       </c>
       <c r="L30" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46900.000000000007</v>
       </c>
       <c r="M30" s="67">
         <f t="shared" si="5"/>
@@ -4503,11 +4507,11 @@
       </c>
       <c r="O30" s="69">
         <f t="shared" si="0"/>
-        <v>422100.25</v>
+        <v>469000.25</v>
       </c>
       <c r="P30" s="70">
         <f t="shared" si="1"/>
-        <v>434763.25</v>
+        <v>483070.25</v>
       </c>
       <c r="Q30" s="40">
         <f t="shared" si="6"/>
@@ -4551,7 +4555,7 @@
       </c>
       <c r="L31" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="M31" s="67">
         <f t="shared" si="5"/>
@@ -4562,11 +4566,11 @@
       </c>
       <c r="O31" s="69">
         <f t="shared" si="0"/>
-        <v>263646.26</v>
+        <v>293846.26</v>
       </c>
       <c r="P31" s="70">
         <f t="shared" si="1"/>
-        <v>271555.26</v>
+        <v>302661.26</v>
       </c>
       <c r="Q31" s="121">
         <f t="shared" si="6"/>
@@ -4611,7 +4615,7 @@
       </c>
       <c r="L32" s="67">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="M32" s="67">
         <f>O$2*F32%</f>
@@ -4622,11 +4626,11 @@
       </c>
       <c r="O32" s="69">
         <f t="shared" si="0"/>
-        <v>13968.27</v>
+        <v>15568.27</v>
       </c>
       <c r="P32" s="70">
         <f t="shared" si="1"/>
-        <v>14387.27</v>
+        <v>16035.27</v>
       </c>
       <c r="Q32" s="40">
         <f t="shared" si="6"/>
@@ -4704,7 +4708,7 @@
       <c r="K34" s="54"/>
       <c r="L34" s="54">
         <f>SUM(L6:L33)</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M34" s="54">
         <f>SUM(M6:M33)</f>
@@ -4716,11 +4720,11 @@
       </c>
       <c r="O34" s="80">
         <f>SUM(O6:O32)</f>
-        <v>11372117.779999999</v>
+        <v>12372117.779999999</v>
       </c>
       <c r="P34" s="80">
         <f>SUM(P6:P32)</f>
-        <v>11713280.779999999</v>
+        <v>12743280.779999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4729,98 +4733,93 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="161" t="s">
+      <c r="D37" s="148" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
-      <c r="G37" s="161"/>
-      <c r="H37" s="161"/>
-      <c r="I37" s="161"/>
-      <c r="J37" s="161"/>
-      <c r="K37" s="161"/>
-      <c r="L37" s="161"/>
-      <c r="M37" s="161"/>
-      <c r="N37" s="161"/>
-      <c r="O37" s="161"/>
+      <c r="E37" s="148"/>
+      <c r="F37" s="148"/>
+      <c r="G37" s="148"/>
+      <c r="H37" s="148"/>
+      <c r="I37" s="148"/>
+      <c r="J37" s="148"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="148"/>
+      <c r="M37" s="148"/>
+      <c r="N37" s="148"/>
+      <c r="O37" s="148"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="161"/>
-      <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
-      <c r="G38" s="161"/>
-      <c r="H38" s="161"/>
-      <c r="I38" s="161"/>
-      <c r="J38" s="161"/>
-      <c r="K38" s="161"/>
-      <c r="L38" s="161"/>
-      <c r="M38" s="161"/>
-      <c r="N38" s="161"/>
-      <c r="O38" s="161"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="148"/>
+      <c r="F38" s="148"/>
+      <c r="G38" s="148"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="148"/>
+      <c r="J38" s="148"/>
+      <c r="K38" s="148"/>
+      <c r="L38" s="148"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="148"/>
+      <c r="O38" s="148"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="161"/>
-      <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
-      <c r="G39" s="161"/>
-      <c r="H39" s="161"/>
-      <c r="I39" s="161"/>
-      <c r="J39" s="161"/>
-      <c r="K39" s="161"/>
-      <c r="L39" s="161"/>
-      <c r="M39" s="161"/>
-      <c r="N39" s="161"/>
-      <c r="O39" s="161"/>
+      <c r="D39" s="148"/>
+      <c r="E39" s="148"/>
+      <c r="F39" s="148"/>
+      <c r="G39" s="148"/>
+      <c r="H39" s="148"/>
+      <c r="I39" s="148"/>
+      <c r="J39" s="148"/>
+      <c r="K39" s="148"/>
+      <c r="L39" s="148"/>
+      <c r="M39" s="148"/>
+      <c r="N39" s="148"/>
+      <c r="O39" s="148"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="161"/>
-      <c r="E40" s="161"/>
-      <c r="F40" s="161"/>
-      <c r="G40" s="161"/>
-      <c r="H40" s="161"/>
-      <c r="I40" s="161"/>
-      <c r="J40" s="161"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="161"/>
-      <c r="M40" s="161"/>
-      <c r="N40" s="161"/>
-      <c r="O40" s="161"/>
+      <c r="D40" s="148"/>
+      <c r="E40" s="148"/>
+      <c r="F40" s="148"/>
+      <c r="G40" s="148"/>
+      <c r="H40" s="148"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="148"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="148"/>
+      <c r="M40" s="148"/>
+      <c r="N40" s="148"/>
+      <c r="O40" s="148"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="161"/>
-      <c r="E41" s="161"/>
-      <c r="F41" s="161"/>
-      <c r="G41" s="161"/>
-      <c r="H41" s="161"/>
-      <c r="I41" s="161"/>
-      <c r="J41" s="161"/>
-      <c r="K41" s="161"/>
-      <c r="L41" s="161"/>
-      <c r="M41" s="161"/>
-      <c r="N41" s="161"/>
-      <c r="O41" s="161"/>
+      <c r="D41" s="148"/>
+      <c r="E41" s="148"/>
+      <c r="F41" s="148"/>
+      <c r="G41" s="148"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="148"/>
+      <c r="J41" s="148"/>
+      <c r="K41" s="148"/>
+      <c r="L41" s="148"/>
+      <c r="M41" s="148"/>
+      <c r="N41" s="148"/>
+      <c r="O41" s="148"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="161"/>
-      <c r="E42" s="161"/>
-      <c r="F42" s="161"/>
-      <c r="G42" s="161"/>
-      <c r="H42" s="161"/>
-      <c r="I42" s="161"/>
-      <c r="J42" s="161"/>
-      <c r="K42" s="161"/>
-      <c r="L42" s="161"/>
-      <c r="M42" s="161"/>
-      <c r="N42" s="161"/>
-      <c r="O42" s="161"/>
+      <c r="D42" s="148"/>
+      <c r="E42" s="148"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="148"/>
+      <c r="H42" s="148"/>
+      <c r="I42" s="148"/>
+      <c r="J42" s="148"/>
+      <c r="K42" s="148"/>
+      <c r="L42" s="148"/>
+      <c r="M42" s="148"/>
+      <c r="N42" s="148"/>
+      <c r="O42" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4833,6 +4832,11 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
+++ b/colombres/Noviembre/Noviembre COLOMBRES 360.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0D6E23-21CC-4C33-8905-5B3BE48FF4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D8814B-4FEE-44F7-BBB3-CA483F333138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1436,6 +1436,48 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1445,46 +1487,46 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1498,48 +1540,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1933,68 +1933,68 @@
       <c r="D3" s="119"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="153" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="163"/>
+      <c r="B4" s="153"/>
       <c r="C4" s="120"/>
       <c r="D4" s="120"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="163"/>
-      <c r="B5" s="163"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="153"/>
       <c r="C5" s="120"/>
       <c r="D5" s="120"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="163"/>
-      <c r="B6" s="163"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
       <c r="C6" s="120"/>
       <c r="D6" s="120"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="163"/>
-      <c r="B7" s="163"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="153"/>
       <c r="C7" s="120"/>
       <c r="D7" s="120"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="150" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="162"/>
+      <c r="B10" s="150"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="162"/>
+      <c r="B11" s="150"/>
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="164" t="s">
+      <c r="A14" s="154" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="164"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="164"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="164"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="164"/>
-      <c r="D16" s="164"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
+      <c r="C16" s="154"/>
+      <c r="D16" s="154"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="164"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="164"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
+      <c r="C17" s="154"/>
+      <c r="D17" s="154"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2068,10 +2068,10 @@
         <v>1008674.64</v>
       </c>
       <c r="D27" s="84"/>
-      <c r="F27" s="160" t="s">
+      <c r="F27" s="148" t="s">
         <v>147</v>
       </c>
-      <c r="G27" s="161"/>
+      <c r="G27" s="149"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -2364,10 +2364,10 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="158" t="s">
+      <c r="A53" s="160" t="s">
         <v>169</v>
       </c>
-      <c r="B53" s="159"/>
+      <c r="B53" s="161"/>
       <c r="C53" s="139">
         <v>177521</v>
       </c>
@@ -2376,10 +2376,10 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="158" t="s">
+      <c r="A54" s="160" t="s">
         <v>168</v>
       </c>
-      <c r="B54" s="159"/>
+      <c r="B54" s="161"/>
       <c r="C54" s="139">
         <v>177521</v>
       </c>
@@ -2492,10 +2492,10 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="156" t="s">
+      <c r="A64" s="158" t="s">
         <v>180</v>
       </c>
-      <c r="B64" s="157"/>
+      <c r="B64" s="159"/>
       <c r="C64" s="139">
         <v>58500</v>
       </c>
@@ -2532,10 +2532,10 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="156" t="s">
+      <c r="A67" s="158" t="s">
         <v>157</v>
       </c>
-      <c r="B67" s="157"/>
+      <c r="B67" s="159"/>
       <c r="C67" s="147">
         <v>68800</v>
       </c>
@@ -2601,11 +2601,11 @@
       <c r="D73" s="97"/>
     </row>
     <row r="74" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="153" t="s">
+      <c r="A74" s="155" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="154"/>
-      <c r="C74" s="155"/>
+      <c r="B74" s="156"/>
+      <c r="C74" s="157"/>
       <c r="D74" s="98">
         <f>9000000-8119017.85</f>
         <v>880982.15000000037</v>
@@ -2738,22 +2738,22 @@
     <row r="94" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="150"/>
-      <c r="B96" s="150"/>
-      <c r="C96" s="150"/>
-      <c r="D96" s="150"/>
+      <c r="A96" s="164"/>
+      <c r="B96" s="164"/>
+      <c r="C96" s="164"/>
+      <c r="D96" s="164"/>
     </row>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="150"/>
-      <c r="B97" s="150"/>
-      <c r="C97" s="150"/>
-      <c r="D97" s="150"/>
+      <c r="A97" s="164"/>
+      <c r="B97" s="164"/>
+      <c r="C97" s="164"/>
+      <c r="D97" s="164"/>
     </row>
     <row r="98" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="150"/>
-      <c r="B98" s="150"/>
-      <c r="C98" s="150"/>
-      <c r="D98" s="150"/>
+      <c r="A98" s="164"/>
+      <c r="B98" s="164"/>
+      <c r="C98" s="164"/>
+      <c r="D98" s="164"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
@@ -2825,14 +2825,14 @@
       <c r="C108" s="40"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="149" t="s">
+      <c r="A110" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="B110" s="149"/>
+      <c r="B110" s="163"/>
     </row>
     <row r="111" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="149"/>
-      <c r="B111" s="149"/>
+      <c r="A111" s="163"/>
+      <c r="B111" s="163"/>
     </row>
     <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="105"/>
@@ -2871,37 +2871,36 @@
       <c r="L119" s="8"/>
     </row>
     <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="148"/>
-      <c r="B120" s="148"/>
-      <c r="C120" s="148"/>
-      <c r="D120" s="148"/>
+      <c r="A120" s="162"/>
+      <c r="B120" s="162"/>
+      <c r="C120" s="162"/>
+      <c r="D120" s="162"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="148"/>
-      <c r="B121" s="148"/>
-      <c r="C121" s="148"/>
-      <c r="D121" s="148"/>
+      <c r="A121" s="162"/>
+      <c r="B121" s="162"/>
+      <c r="C121" s="162"/>
+      <c r="D121" s="162"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="148"/>
-      <c r="B122" s="148"/>
-      <c r="C122" s="148"/>
-      <c r="D122" s="148"/>
+      <c r="A122" s="162"/>
+      <c r="B122" s="162"/>
+      <c r="C122" s="162"/>
+      <c r="D122" s="162"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="148"/>
-      <c r="B123" s="148"/>
-      <c r="C123" s="148"/>
-      <c r="D123" s="148"/>
+      <c r="A123" s="162"/>
+      <c r="B123" s="162"/>
+      <c r="C123" s="162"/>
+      <c r="D123" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A14:D17"/>
+    <mergeCell ref="A120:D123"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A96:D98"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A53:B53"/>
@@ -2911,11 +2910,12 @@
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A120:D123"/>
-    <mergeCell ref="A110:B111"/>
-    <mergeCell ref="A96:D98"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A4:B7"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A14:D17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2951,18 +2951,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="171" t="s">
+      <c r="B1" s="165" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="165"/>
+      <c r="K1" s="165"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2971,16 +2971,16 @@
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="172"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="172"/>
-      <c r="I3" s="172"/>
-      <c r="J3" s="172"/>
-      <c r="K3" s="172"/>
+      <c r="B3" s="166"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+      <c r="J3" s="166"/>
+      <c r="K3" s="166"/>
       <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
@@ -3015,10 +3015,10 @@
       <c r="P3" s="52"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="165" t="s">
+      <c r="A4" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="167" t="s">
+      <c r="B4" s="181" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="169" t="s">
@@ -3042,49 +3042,49 @@
       <c r="I4" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="176" t="s">
+      <c r="L4" s="171" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="N4" s="177" t="s">
         <v>87</v>
       </c>
       <c r="O4" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="173" t="s">
+      <c r="P4" s="167" t="s">
         <v>85</v>
       </c>
       <c r="S4" s="40"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="166"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="179"/>
-      <c r="K5" s="177"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="177"/>
-      <c r="N5" s="182"/>
+      <c r="A5" s="180"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
+      <c r="H5" s="173"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="178"/>
       <c r="O5" s="53" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/12</v>
       </c>
-      <c r="P5" s="174"/>
+      <c r="P5" s="168"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -4733,93 +4733,98 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="148" t="s">
+      <c r="D37" s="162" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
-      <c r="H37" s="148"/>
-      <c r="I37" s="148"/>
-      <c r="J37" s="148"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="148"/>
-      <c r="M37" s="148"/>
-      <c r="N37" s="148"/>
-      <c r="O37" s="148"/>
+      <c r="E37" s="162"/>
+      <c r="F37" s="162"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="162"/>
+      <c r="K37" s="162"/>
+      <c r="L37" s="162"/>
+      <c r="M37" s="162"/>
+      <c r="N37" s="162"/>
+      <c r="O37" s="162"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="148"/>
-      <c r="E38" s="148"/>
-      <c r="F38" s="148"/>
-      <c r="G38" s="148"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="148"/>
-      <c r="J38" s="148"/>
-      <c r="K38" s="148"/>
-      <c r="L38" s="148"/>
-      <c r="M38" s="148"/>
-      <c r="N38" s="148"/>
-      <c r="O38" s="148"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="162"/>
+      <c r="K38" s="162"/>
+      <c r="L38" s="162"/>
+      <c r="M38" s="162"/>
+      <c r="N38" s="162"/>
+      <c r="O38" s="162"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="148"/>
-      <c r="E39" s="148"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="148"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="148"/>
-      <c r="L39" s="148"/>
-      <c r="M39" s="148"/>
-      <c r="N39" s="148"/>
-      <c r="O39" s="148"/>
+      <c r="D39" s="162"/>
+      <c r="E39" s="162"/>
+      <c r="F39" s="162"/>
+      <c r="G39" s="162"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="162"/>
+      <c r="J39" s="162"/>
+      <c r="K39" s="162"/>
+      <c r="L39" s="162"/>
+      <c r="M39" s="162"/>
+      <c r="N39" s="162"/>
+      <c r="O39" s="162"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="148"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="148"/>
-      <c r="H40" s="148"/>
-      <c r="I40" s="148"/>
-      <c r="J40" s="148"/>
-      <c r="K40" s="148"/>
-      <c r="L40" s="148"/>
-      <c r="M40" s="148"/>
-      <c r="N40" s="148"/>
-      <c r="O40" s="148"/>
+      <c r="D40" s="162"/>
+      <c r="E40" s="162"/>
+      <c r="F40" s="162"/>
+      <c r="G40" s="162"/>
+      <c r="H40" s="162"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="162"/>
+      <c r="K40" s="162"/>
+      <c r="L40" s="162"/>
+      <c r="M40" s="162"/>
+      <c r="N40" s="162"/>
+      <c r="O40" s="162"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="148"/>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="148"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="148"/>
-      <c r="N41" s="148"/>
-      <c r="O41" s="148"/>
+      <c r="D41" s="162"/>
+      <c r="E41" s="162"/>
+      <c r="F41" s="162"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="162"/>
+      <c r="I41" s="162"/>
+      <c r="J41" s="162"/>
+      <c r="K41" s="162"/>
+      <c r="L41" s="162"/>
+      <c r="M41" s="162"/>
+      <c r="N41" s="162"/>
+      <c r="O41" s="162"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
-      <c r="H42" s="148"/>
-      <c r="I42" s="148"/>
-      <c r="J42" s="148"/>
-      <c r="K42" s="148"/>
-      <c r="L42" s="148"/>
-      <c r="M42" s="148"/>
-      <c r="N42" s="148"/>
-      <c r="O42" s="148"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="162"/>
+      <c r="K42" s="162"/>
+      <c r="L42" s="162"/>
+      <c r="M42" s="162"/>
+      <c r="N42" s="162"/>
+      <c r="O42" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4832,11 +4837,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
